--- a/Gantt_VERIFEX.xlsx
+++ b/Gantt_VERIFEX.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gantt VERIFEX" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Gantt VERIFEX'!$A$1:$I$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Gantt VERIFEX'!$A$1:$I$48</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -638,7 +638,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I54"/>
+  <dimension ref="A1:I55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -721,7 +721,7 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Definicion de historias de usuario</t>
+          <t>Definicion de 10 historias de usuario (HU-01 a HU-10)</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
@@ -733,10 +733,10 @@
         <v>45901</v>
       </c>
       <c r="F3" s="7" t="n">
-        <v>45909</v>
+        <v>45911</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H3" s="5" t="n"/>
       <c r="I3" s="8" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Definicion de requisitos funcionales</t>
+          <t>Definicion de requisitos funcionales y no funcionales</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
@@ -761,13 +761,13 @@
         </is>
       </c>
       <c r="E4" s="7" t="n">
-        <v>45910</v>
+        <v>45912</v>
       </c>
       <c r="F4" s="7" t="n">
-        <v>45916</v>
+        <v>45920</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H4" s="5" t="inlineStr">
         <is>
@@ -787,22 +787,22 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Definicion de requisitos no funcionales</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>Marco</t>
+          <t>Creacion de diagramas UML (casos de uso, actividades, secuencia, clases, ER)</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>Tony</t>
         </is>
       </c>
       <c r="E5" s="7" t="n">
-        <v>45917</v>
+        <v>45921</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>45921</v>
+        <v>45933</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
@@ -816,54 +816,54 @@
       </c>
     </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="4" t="n"/>
-      <c r="B6" s="5" t="n">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Fase 2: Diseno (Wireframes, Mockups, Arquitectura)</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n"/>
+      <c r="C6" s="3" t="n"/>
+      <c r="D6" s="3" t="n"/>
+      <c r="E6" s="3" t="n"/>
+      <c r="F6" s="3" t="n"/>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
+      <c r="I6" s="3" t="n"/>
+    </row>
+    <row r="7" ht="24" customHeight="1">
+      <c r="A7" s="4" t="n"/>
+      <c r="B7" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Validacion de historias de usuario con asesores</t>
-        </is>
-      </c>
-      <c r="D6" s="9" t="inlineStr">
-        <is>
-          <t>Tony</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="n">
-        <v>45922</v>
-      </c>
-      <c r="F6" s="7" t="n">
-        <v>45926</v>
-      </c>
-      <c r="G6" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Diseno de wireframes y mockups de interfaz</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>Luis</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="n">
+        <v>45934</v>
+      </c>
+      <c r="F7" s="7" t="n">
+        <v>45944</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I6" s="8" t="inlineStr">
-        <is>
-          <t>Completado</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Fase 2: Diseno (Wireframes, Mockups, Arquitectura)</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="n"/>
-      <c r="C7" s="3" t="n"/>
-      <c r="D7" s="3" t="n"/>
-      <c r="E7" s="3" t="n"/>
-      <c r="F7" s="3" t="n"/>
-      <c r="G7" s="3" t="n"/>
-      <c r="H7" s="3" t="n"/>
-      <c r="I7" s="3" t="n"/>
+      <c r="I7" s="8" t="inlineStr">
+        <is>
+          <t>Completado</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="4" t="n"/>
@@ -872,7 +872,7 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Diseno de wireframes (baja fidelidad)</t>
+          <t>Seleccion de paleta de colores y fuentes tipograficas (Orbitron, Rajdhani, Share Tech Mono)</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr">
@@ -881,13 +881,13 @@
         </is>
       </c>
       <c r="E8" s="7" t="n">
-        <v>45927</v>
+        <v>45945</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>45935</v>
+        <v>45950</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
@@ -907,22 +907,22 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Diseno de mockups (alta fidelidad)</t>
-        </is>
-      </c>
-      <c r="D9" s="10" t="inlineStr">
-        <is>
-          <t>Luis</t>
+          <t>Diseno de arquitectura cliente-servidor (React + Flask)</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>Marco</t>
         </is>
       </c>
       <c r="E9" s="7" t="n">
-        <v>45936</v>
+        <v>45951</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>45946</v>
+        <v>45959</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
@@ -936,98 +936,100 @@
       </c>
     </row>
     <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="4" t="n"/>
-      <c r="B10" s="5" t="n">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Fase 3: Desarrollo</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n"/>
+      <c r="C10" s="3" t="n"/>
+      <c r="D10" s="3" t="n"/>
+      <c r="E10" s="3" t="n"/>
+      <c r="F10" s="3" t="n"/>
+      <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
+      <c r="I10" s="3" t="n"/>
+    </row>
+    <row r="11" ht="24" customHeight="1">
+      <c r="A11" s="4" t="n"/>
+      <c r="B11" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>Diseno de arquitectura (cliente-servidor)</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Setup del proyecto (Vite + React + TypeScript + Tailwind + PostCSS)</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
         <is>
           <t>Marco</t>
         </is>
       </c>
-      <c r="E10" s="7" t="n">
-        <v>45947</v>
-      </c>
-      <c r="F10" s="7" t="n">
-        <v>45955</v>
-      </c>
-      <c r="G10" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="H10" s="5" t="inlineStr">
+      <c r="E11" s="7" t="n">
+        <v>45960</v>
+      </c>
+      <c r="F11" s="7" t="n">
+        <v>45965</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I10" s="8" t="inlineStr">
-        <is>
-          <t>Completado</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>Fase 3: Desarrollo</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="n"/>
-      <c r="C11" s="3" t="n"/>
-      <c r="D11" s="3" t="n"/>
-      <c r="E11" s="3" t="n"/>
-      <c r="F11" s="3" t="n"/>
-      <c r="G11" s="3" t="n"/>
-      <c r="H11" s="3" t="n"/>
-      <c r="I11" s="3" t="n"/>
+      <c r="I11" s="8" t="inlineStr">
+        <is>
+          <t>Completado</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="4" t="n"/>
-      <c r="B12" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>Setup del proyecto (Vite + React + TypeScript)</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>Marco</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="n">
-        <v>45956</v>
-      </c>
-      <c r="F12" s="7" t="n">
-        <v>45962</v>
-      </c>
-      <c r="G12" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="H12" s="5" t="inlineStr">
+      <c r="A12" s="11" t="n"/>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>v0.0.1 - Esqueleto del proyecto con Vite, React, TypeScript y Tailwind configurados</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="n">
+        <v>45966</v>
+      </c>
+      <c r="F12" s="13" t="n">
+        <v>45967</v>
+      </c>
+      <c r="G12" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H12" s="12" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="I12" s="8" t="inlineStr">
-        <is>
-          <t>Completado</t>
+      <c r="I12" s="12" t="inlineStr">
+        <is>
+          <t>Lanzado</t>
         </is>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1">
       <c r="A13" s="4" t="n"/>
       <c r="B13" s="5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Setup del backend (Flask + Python)</t>
+          <t>Setup del backend (Flask + CORS + rutas /analyze y /health)</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
@@ -1036,17 +1038,17 @@
         </is>
       </c>
       <c r="E13" s="7" t="n">
-        <v>45963</v>
+        <v>45966</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>45969</v>
+        <v>45971</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I13" s="8" t="inlineStr">
@@ -1058,11 +1060,11 @@
     <row r="14" ht="24" customHeight="1">
       <c r="A14" s="4" t="n"/>
       <c r="B14" s="5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Implementacion del scraper (BeautifulSoup)</t>
+          <t>Implementacion del scraper de URLs con BeautifulSoup (scrape_url)</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
@@ -1071,17 +1073,17 @@
         </is>
       </c>
       <c r="E14" s="7" t="n">
-        <v>45970</v>
+        <v>45972</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>45986</v>
+        <v>45982</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I14" s="8" t="inlineStr">
@@ -1108,17 +1110,17 @@
         </is>
       </c>
       <c r="E15" s="13" t="n">
-        <v>45987</v>
+        <v>45983</v>
       </c>
       <c r="F15" s="13" t="n">
-        <v>45988</v>
+        <v>45984</v>
       </c>
       <c r="G15" s="12" t="n">
         <v>2</v>
       </c>
       <c r="H15" s="12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I15" s="12" t="inlineStr">
@@ -1130,670 +1132,670 @@
     <row r="16" ht="24" customHeight="1">
       <c r="A16" s="4" t="n"/>
       <c r="B16" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Integracion con Groq API (call_groq con fallback a multiples modelos)</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>Marco</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>45983</v>
+      </c>
+      <c r="F16" s="7" t="n">
+        <v>45993</v>
+      </c>
+      <c r="G16" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>Integracion con Groq API</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I16" s="8" t="inlineStr">
+        <is>
+          <t>Completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="24" customHeight="1">
+      <c r="A17" s="4" t="n"/>
+      <c r="B17" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Implementacion de prompt engineering (SYSTEM_PROMPT con clasificacion)</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
         <is>
           <t>Marco</t>
         </is>
       </c>
-      <c r="E16" s="7" t="n">
-        <v>45987</v>
-      </c>
-      <c r="F16" s="7" t="n">
+      <c r="E17" s="7" t="n">
+        <v>45994</v>
+      </c>
+      <c r="F17" s="7" t="n">
+        <v>46002</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I17" s="8" t="inlineStr">
+        <is>
+          <t>Completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="24" customHeight="1">
+      <c r="A18" s="11" t="n"/>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>v0.2.0 - Analisis con IA via Groq API implementado</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E18" s="13" t="n">
         <v>46003</v>
       </c>
-      <c r="G16" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I16" s="8" t="inlineStr">
-        <is>
-          <t>Completado</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="11" t="n"/>
-      <c r="B17" s="12" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="C17" s="11" t="inlineStr">
-        <is>
-          <t>v0.2.0 - Analisis con IA via Groq API implementado</t>
-        </is>
-      </c>
-      <c r="D17" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E17" s="13" t="n">
+      <c r="F18" s="13" t="n">
         <v>46004</v>
       </c>
-      <c r="F17" s="13" t="n">
-        <v>46005</v>
-      </c>
-      <c r="G17" s="12" t="n">
+      <c r="G18" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H17" s="12" t="inlineStr">
+      <c r="H18" s="12" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="I17" s="12" t="inlineStr">
+      <c r="I18" s="12" t="inlineStr">
         <is>
           <t>Lanzado</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="4" t="n"/>
-      <c r="B18" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>Implementacion del prompt engineering</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t>Marco</t>
-        </is>
-      </c>
-      <c r="E18" s="7" t="n">
-        <v>46004</v>
-      </c>
-      <c r="F18" s="7" t="n">
-        <v>46014</v>
-      </c>
-      <c r="G18" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="H18" s="5" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="I18" s="8" t="inlineStr">
-        <is>
-          <t>Completado</t>
         </is>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1">
       <c r="A19" s="4" t="n"/>
       <c r="B19" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Implementacion del clasificador de credibilidad (analyze_url con 5 categorias)</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>Marco</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="n">
+        <v>46003</v>
+      </c>
+      <c r="F19" s="7" t="n">
+        <v>46015</v>
+      </c>
+      <c r="G19" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>Clasificador de credibilidad (REAL, FALSO, etc.)</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="I19" s="8" t="inlineStr">
+        <is>
+          <t>Completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="24" customHeight="1">
+      <c r="A20" s="4" t="n"/>
+      <c r="B20" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>Implementacion de lista de dominios confiables (CREDIBLE_DOMAINS, 29 fuentes)</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
         <is>
           <t>Marco</t>
         </is>
       </c>
-      <c r="E19" s="7" t="n">
-        <v>46015</v>
-      </c>
-      <c r="F19" s="7" t="n">
-        <v>46031</v>
-      </c>
-      <c r="G19" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="H19" s="5" t="inlineStr">
+      <c r="E20" s="7" t="n">
+        <v>46016</v>
+      </c>
+      <c r="F20" s="7" t="n">
+        <v>46020</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I19" s="8" t="inlineStr">
-        <is>
-          <t>Completado</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="11" t="n"/>
-      <c r="B20" s="12" t="inlineStr">
+      <c r="I20" s="8" t="inlineStr">
+        <is>
+          <t>Completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="24" customHeight="1">
+      <c r="A21" s="11" t="n"/>
+      <c r="B21" s="12" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="C20" s="11" t="inlineStr">
-        <is>
-          <t>v0.3.0 - Clasificador de credibilidad funcional (REAL, FALSO, SATIRA, etc.)</t>
-        </is>
-      </c>
-      <c r="D20" s="12" t="inlineStr">
+      <c r="C21" s="11" t="inlineStr">
+        <is>
+          <t>v0.3.0 - Clasificador de credibilidad funcional (REAL, FALSO, SATIRA, ESTAFA, NO VERIFICABLE)</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E20" s="13" t="n">
-        <v>46032</v>
-      </c>
-      <c r="F20" s="13" t="n">
-        <v>46033</v>
-      </c>
-      <c r="G20" s="12" t="n">
+      <c r="E21" s="13" t="n">
+        <v>46021</v>
+      </c>
+      <c r="F21" s="13" t="n">
+        <v>46022</v>
+      </c>
+      <c r="G21" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H20" s="12" t="inlineStr">
+      <c r="H21" s="12" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="I20" s="12" t="inlineStr">
+      <c r="I21" s="12" t="inlineStr">
         <is>
           <t>Lanzado</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="24" customHeight="1">
-      <c r="A21" s="4" t="n"/>
-      <c r="B21" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>Busqueda de noticias similares (Google News RSS)</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>Marco</t>
-        </is>
-      </c>
-      <c r="E21" s="7" t="n">
-        <v>46032</v>
-      </c>
-      <c r="F21" s="7" t="n">
-        <v>46042</v>
-      </c>
-      <c r="G21" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="H21" s="5" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="I21" s="8" t="inlineStr">
-        <is>
-          <t>Completado</t>
         </is>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1">
       <c r="A22" s="4" t="n"/>
       <c r="B22" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>Busqueda de noticias similares via Google News RSS (news_finder.py)</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>Marco</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="n">
+        <v>46021</v>
+      </c>
+      <c r="F22" s="7" t="n">
+        <v>46029</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="I22" s="8" t="inlineStr">
+        <is>
+          <t>Completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="24" customHeight="1">
+      <c r="A23" s="4" t="n"/>
+      <c r="B23" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>Conexion frontend-backend (API REST)</t>
-        </is>
-      </c>
-      <c r="D22" s="6" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>Conexion frontend-backend via API REST (fetch /analyze con AbortController)</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
         <is>
           <t>Marco</t>
         </is>
       </c>
-      <c r="E22" s="7" t="n">
-        <v>46043</v>
-      </c>
-      <c r="F22" s="7" t="n">
-        <v>46055</v>
-      </c>
-      <c r="G22" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="H22" s="5" t="inlineStr">
+      <c r="E23" s="7" t="n">
+        <v>46030</v>
+      </c>
+      <c r="F23" s="7" t="n">
+        <v>46038</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="I22" s="8" t="inlineStr">
-        <is>
-          <t>Completado</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="24" customHeight="1">
-      <c r="A23" s="11" t="n"/>
-      <c r="B23" s="12" t="inlineStr">
+      <c r="I23" s="8" t="inlineStr">
+        <is>
+          <t>Completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="24" customHeight="1">
+      <c r="A24" s="11" t="n"/>
+      <c r="B24" s="12" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="C23" s="11" t="inlineStr">
+      <c r="C24" s="11" t="inlineStr">
         <is>
           <t>v0.4.0 - Frontend conectado al backend via API REST</t>
         </is>
       </c>
-      <c r="D23" s="12" t="inlineStr">
+      <c r="D24" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E23" s="13" t="n">
-        <v>46056</v>
-      </c>
-      <c r="F23" s="13" t="n">
-        <v>46057</v>
-      </c>
-      <c r="G23" s="12" t="n">
+      <c r="E24" s="13" t="n">
+        <v>46039</v>
+      </c>
+      <c r="F24" s="13" t="n">
+        <v>46040</v>
+      </c>
+      <c r="G24" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H23" s="12" t="inlineStr">
+      <c r="H24" s="12" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="I23" s="12" t="inlineStr">
+      <c r="I24" s="12" t="inlineStr">
         <is>
           <t>Lanzado</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="24" customHeight="1">
-      <c r="A24" s="4" t="n"/>
-      <c r="B24" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>Implementacion de componentes base (UI)</t>
-        </is>
-      </c>
-      <c r="D24" s="10" t="inlineStr">
-        <is>
-          <t>Luis</t>
-        </is>
-      </c>
-      <c r="E24" s="7" t="n">
-        <v>46056</v>
-      </c>
-      <c r="F24" s="7" t="n">
-        <v>46072</v>
-      </c>
-      <c r="G24" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="H24" s="5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="I24" s="8" t="inlineStr">
-        <is>
-          <t>Completado</t>
         </is>
       </c>
     </row>
     <row r="25" ht="24" customHeight="1">
       <c r="A25" s="4" t="n"/>
       <c r="B25" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Implementacion de componentes base (UrlInput, VerdictDisplay, ConfidenceBar, RedFlags, SimilarNews, LanguageToggle)</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="inlineStr">
+        <is>
+          <t>Luis</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="n">
+        <v>46039</v>
+      </c>
+      <c r="F25" s="7" t="n">
+        <v>46053</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="I25" s="8" t="inlineStr">
+        <is>
+          <t>Completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="24" customHeight="1">
+      <c r="A26" s="4" t="n"/>
+      <c r="B26" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>Implementacion de estados (loading, error, results)</t>
-        </is>
-      </c>
-      <c r="D25" s="10" t="inlineStr">
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>Implementacion de manejo de estados (loading, error, results) en App.tsx</t>
+        </is>
+      </c>
+      <c r="D26" s="10" t="inlineStr">
         <is>
           <t>Luis</t>
         </is>
       </c>
-      <c r="E25" s="7" t="n">
+      <c r="E26" s="7" t="n">
+        <v>46054</v>
+      </c>
+      <c r="F26" s="7" t="n">
+        <v>46062</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="I26" s="8" t="inlineStr">
+        <is>
+          <t>Completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="24" customHeight="1">
+      <c r="A27" s="11" t="n"/>
+      <c r="B27" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="C27" s="11" t="inlineStr">
+        <is>
+          <t>v0.5.0 - UI completa con todos los componentes, estados y noticias similares</t>
+        </is>
+      </c>
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E27" s="13" t="n">
+        <v>46063</v>
+      </c>
+      <c r="F27" s="13" t="n">
+        <v>46064</v>
+      </c>
+      <c r="G27" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H27" s="12" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="I27" s="12" t="inlineStr">
+        <is>
+          <t>Lanzado</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="24" customHeight="1">
+      <c r="A28" s="4" t="n"/>
+      <c r="B28" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>Implementacion de soporte bilingue ES/EN en todos los componentes</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="inlineStr">
+        <is>
+          <t>Luis</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="n">
+        <v>46063</v>
+      </c>
+      <c r="F28" s="7" t="n">
+        <v>46071</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="I28" s="8" t="inlineStr">
+        <is>
+          <t>Completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="24" customHeight="1">
+      <c r="A29" s="11" t="n"/>
+      <c r="B29" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="C29" s="11" t="inlineStr">
+        <is>
+          <t>v0.6.0 - Soporte bilingue ES/EN implementado</t>
+        </is>
+      </c>
+      <c r="D29" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E29" s="13" t="n">
+        <v>46072</v>
+      </c>
+      <c r="F29" s="13" t="n">
         <v>46073</v>
       </c>
-      <c r="F25" s="7" t="n">
-        <v>46085</v>
-      </c>
-      <c r="G25" s="5" t="n">
+      <c r="G29" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H29" s="12" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="I29" s="12" t="inlineStr">
+        <is>
+          <t>Lanzado</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="24" customHeight="1">
+      <c r="A30" s="4" t="n"/>
+      <c r="B30" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>Implementacion de article_type (5 tipos) y deteccion de estafas (is_scam)</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>Marco</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="n">
+        <v>46072</v>
+      </c>
+      <c r="F30" s="7" t="n">
+        <v>46080</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="I30" s="8" t="inlineStr">
+        <is>
+          <t>Completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="24" customHeight="1">
+      <c r="A31" s="11" t="n"/>
+      <c r="B31" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="inlineStr">
+        <is>
+          <t>v0.7.0 - Clasificacion avanzada: tipo de articulo y deteccion de estafas</t>
+        </is>
+      </c>
+      <c r="D31" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E31" s="13" t="n">
+        <v>46081</v>
+      </c>
+      <c r="F31" s="13" t="n">
+        <v>46082</v>
+      </c>
+      <c r="G31" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H31" s="12" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="I31" s="12" t="inlineStr">
+        <is>
+          <t>Lanzado</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="24" customHeight="1">
+      <c r="A32" s="4" t="n"/>
+      <c r="B32" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>Diseno visual cyberpunk: animacion de cuadricula, efecto glitch, vignette CRT, scanlines, clip-paths</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="inlineStr">
+        <is>
+          <t>Luis</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="n">
+        <v>46081</v>
+      </c>
+      <c r="F32" s="7" t="n">
+        <v>46093</v>
+      </c>
+      <c r="G32" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="I25" s="8" t="inlineStr">
-        <is>
-          <t>Completado</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="24" customHeight="1">
-      <c r="A26" s="11" t="n"/>
-      <c r="B26" s="12" t="inlineStr">
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="I32" s="8" t="inlineStr">
+        <is>
+          <t>Completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="24" customHeight="1">
+      <c r="A33" s="11" t="n"/>
+      <c r="B33" s="12" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="C26" s="11" t="inlineStr">
-        <is>
-          <t>v0.5.0 - UI completa con resultados, noticias similares y estados</t>
-        </is>
-      </c>
-      <c r="D26" s="12" t="inlineStr">
+      <c r="C33" s="11" t="inlineStr">
+        <is>
+          <t>v0.8.0 - Diseno visual cyberpunk finalizado</t>
+        </is>
+      </c>
+      <c r="D33" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E26" s="13" t="n">
-        <v>46086</v>
-      </c>
-      <c r="F26" s="13" t="n">
-        <v>46087</v>
-      </c>
-      <c r="G26" s="12" t="n">
+      <c r="E33" s="13" t="n">
+        <v>46094</v>
+      </c>
+      <c r="F33" s="13" t="n">
+        <v>46095</v>
+      </c>
+      <c r="G33" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H26" s="12" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="I26" s="12" t="inlineStr">
+      <c r="H33" s="12" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="I33" s="12" t="inlineStr">
         <is>
           <t>Lanzado</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="24" customHeight="1">
-      <c r="A27" s="4" t="n"/>
-      <c r="B27" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>Soporte bilingue (espanol/ingles)</t>
-        </is>
-      </c>
-      <c r="D27" s="10" t="inlineStr">
-        <is>
-          <t>Luis</t>
-        </is>
-      </c>
-      <c r="E27" s="7" t="n">
-        <v>46086</v>
-      </c>
-      <c r="F27" s="7" t="n">
-        <v>46096</v>
-      </c>
-      <c r="G27" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="H27" s="5" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="I27" s="8" t="inlineStr">
-        <is>
-          <t>Completado</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="24" customHeight="1">
-      <c r="A28" s="11" t="n"/>
-      <c r="B28" s="12" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="C28" s="11" t="inlineStr">
-        <is>
-          <t>v0.6.0 - Soporte bilingue ES/EN implementado</t>
-        </is>
-      </c>
-      <c r="D28" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E28" s="13" t="n">
-        <v>46097</v>
-      </c>
-      <c r="F28" s="13" t="n">
-        <v>46098</v>
-      </c>
-      <c r="G28" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="H28" s="12" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="I28" s="12" t="inlineStr">
-        <is>
-          <t>Lanzado</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="24" customHeight="1">
-      <c r="A29" s="4" t="n"/>
-      <c r="B29" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>Implementacion de article_type y deteccion de estafas</t>
-        </is>
-      </c>
-      <c r="D29" s="6" t="inlineStr">
-        <is>
-          <t>Marco</t>
-        </is>
-      </c>
-      <c r="E29" s="7" t="n">
-        <v>46097</v>
-      </c>
-      <c r="F29" s="7" t="n">
-        <v>46107</v>
-      </c>
-      <c r="G29" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="H29" s="5" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="I29" s="8" t="inlineStr">
-        <is>
-          <t>Completado</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="24" customHeight="1">
-      <c r="A30" s="11" t="n"/>
-      <c r="B30" s="12" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="C30" s="11" t="inlineStr">
-        <is>
-          <t>v0.7.0 - Clasificacion avanzada: tipo de articulo y deteccion de estafas</t>
-        </is>
-      </c>
-      <c r="D30" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E30" s="13" t="n">
-        <v>46108</v>
-      </c>
-      <c r="F30" s="13" t="n">
-        <v>46109</v>
-      </c>
-      <c r="G30" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="H30" s="12" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="I30" s="12" t="inlineStr">
-        <is>
-          <t>Lanzado</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="24" customHeight="1">
-      <c r="A31" s="4" t="n"/>
-      <c r="B31" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>Diseno visual cyberpunk / UI final</t>
-        </is>
-      </c>
-      <c r="D31" s="10" t="inlineStr">
-        <is>
-          <t>Luis</t>
-        </is>
-      </c>
-      <c r="E31" s="7" t="n">
-        <v>46108</v>
-      </c>
-      <c r="F31" s="7" t="n">
-        <v>46122</v>
-      </c>
-      <c r="G31" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="H31" s="5" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="I31" s="8" t="inlineStr">
-        <is>
-          <t>Completado</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="24" customHeight="1">
-      <c r="A32" s="11" t="n"/>
-      <c r="B32" s="12" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="C32" s="11" t="inlineStr">
-        <is>
-          <t>v0.8.0 - Diseno visual cyberpunk finalizado</t>
-        </is>
-      </c>
-      <c r="D32" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E32" s="13" t="n">
-        <v>46123</v>
-      </c>
-      <c r="F32" s="13" t="n">
-        <v>46124</v>
-      </c>
-      <c r="G32" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="H32" s="12" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="I32" s="12" t="inlineStr">
-        <is>
-          <t>Lanzado</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="24" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="34" ht="24" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>Fase 4: Pruebas y Despliegue</t>
         </is>
       </c>
-      <c r="B33" s="3" t="n"/>
-      <c r="C33" s="3" t="n"/>
-      <c r="D33" s="3" t="n"/>
-      <c r="E33" s="3" t="n"/>
-      <c r="F33" s="3" t="n"/>
-      <c r="G33" s="3" t="n"/>
-      <c r="H33" s="3" t="n"/>
-      <c r="I33" s="3" t="n"/>
-    </row>
-    <row r="34" ht="24" customHeight="1">
-      <c r="A34" s="4" t="n"/>
-      <c r="B34" s="5" t="n">
-        <v>21</v>
-      </c>
-      <c r="C34" s="4" t="inlineStr">
-        <is>
-          <t>Correccion de errores y timeouts</t>
-        </is>
-      </c>
-      <c r="D34" s="6" t="inlineStr">
-        <is>
-          <t>Marco</t>
-        </is>
-      </c>
-      <c r="E34" s="7" t="n">
-        <v>46123</v>
-      </c>
-      <c r="F34" s="7" t="n">
-        <v>46139</v>
-      </c>
-      <c r="G34" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="H34" s="5" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="I34" s="8" t="inlineStr">
-        <is>
-          <t>Completado</t>
-        </is>
-      </c>
+      <c r="B34" s="3" t="n"/>
+      <c r="C34" s="3" t="n"/>
+      <c r="D34" s="3" t="n"/>
+      <c r="E34" s="3" t="n"/>
+      <c r="F34" s="3" t="n"/>
+      <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n"/>
+      <c r="I34" s="3" t="n"/>
     </row>
     <row r="35" ht="24" customHeight="1">
       <c r="A35" s="4" t="n"/>
       <c r="B35" s="5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Configuracion de despliegue (Procfile, gunicorn)</t>
+          <t>Creacion de suite de pruebas backend (server/test_analyzer.py, pytest)</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
@@ -1802,17 +1804,17 @@
         </is>
       </c>
       <c r="E35" s="7" t="n">
-        <v>46140</v>
+        <v>46094</v>
       </c>
       <c r="F35" s="7" t="n">
-        <v>46145</v>
+        <v>46104</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I35" s="8" t="inlineStr">
@@ -1824,11 +1826,11 @@
     <row r="36" ht="24" customHeight="1">
       <c r="A36" s="4" t="n"/>
       <c r="B36" s="5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Despliegue en Railway (fallo, migracion a Render)</t>
+          <t>Creacion de suite de pruebas frontend (vitest + testing-library, 7 archivos, 52 tests)</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
@@ -1837,17 +1839,17 @@
         </is>
       </c>
       <c r="E36" s="7" t="n">
-        <v>46146</v>
+        <v>46105</v>
       </c>
       <c r="F36" s="7" t="n">
-        <v>46153</v>
+        <v>46115</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H36" s="5" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I36" s="8" t="inlineStr">
@@ -1859,11 +1861,11 @@
     <row r="37" ht="24" customHeight="1">
       <c r="A37" s="4" t="n"/>
       <c r="B37" s="5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Configuracion de CORS, PORT, variables de entorno</t>
+          <t>Configuracion de despliegue (Procfile con gunicorn, variables de entorno, CORS)</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
@@ -1872,17 +1874,17 @@
         </is>
       </c>
       <c r="E37" s="7" t="n">
-        <v>46154</v>
+        <v>46116</v>
       </c>
       <c r="F37" s="7" t="n">
-        <v>46159</v>
+        <v>46121</v>
       </c>
       <c r="G37" s="5" t="n">
         <v>6</v>
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I37" s="8" t="inlineStr">
@@ -1894,376 +1896,411 @@
     <row r="38" ht="24" customHeight="1">
       <c r="A38" s="4" t="n"/>
       <c r="B38" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>Despliegue en Railway (fallo por limitaciones, migracion a Render)</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>Marco</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="n">
+        <v>46122</v>
+      </c>
+      <c r="F38" s="7" t="n">
+        <v>46129</v>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="H38" s="5" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="I38" s="8" t="inlineStr">
+        <is>
+          <t>Completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="24" customHeight="1">
+      <c r="A39" s="4" t="n"/>
+      <c r="B39" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="C38" s="4" t="inlineStr">
-        <is>
-          <t>Despliegue exitoso en Render</t>
-        </is>
-      </c>
-      <c r="D38" s="6" t="inlineStr">
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>Despliegue exitoso en Render con dominio publico</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
         <is>
           <t>Marco</t>
         </is>
       </c>
-      <c r="E38" s="7" t="n">
-        <v>46160</v>
-      </c>
-      <c r="F38" s="7" t="n">
-        <v>46172</v>
-      </c>
-      <c r="G38" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="H38" s="5" t="inlineStr">
+      <c r="E39" s="7" t="n">
+        <v>46130</v>
+      </c>
+      <c r="F39" s="7" t="n">
+        <v>46138</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="I38" s="8" t="inlineStr">
-        <is>
-          <t>Completado</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="24" customHeight="1">
-      <c r="A39" s="11" t="n"/>
-      <c r="B39" s="12" t="inlineStr">
+      <c r="I39" s="8" t="inlineStr">
+        <is>
+          <t>Completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="24" customHeight="1">
+      <c r="A40" s="11" t="n"/>
+      <c r="B40" s="12" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="C39" s="11" t="inlineStr">
+      <c r="C40" s="11" t="inlineStr">
         <is>
           <t>v1.0.0 - Version estable desplegada en Render con dominio publico</t>
         </is>
       </c>
-      <c r="D39" s="12" t="inlineStr">
+      <c r="D40" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E39" s="13" t="n">
-        <v>46173</v>
-      </c>
-      <c r="F39" s="13" t="n">
-        <v>46174</v>
-      </c>
-      <c r="G39" s="12" t="n">
+      <c r="E40" s="13" t="n">
+        <v>46139</v>
+      </c>
+      <c r="F40" s="13" t="n">
+        <v>46140</v>
+      </c>
+      <c r="G40" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H39" s="12" t="inlineStr">
+      <c r="H40" s="12" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="I39" s="12" t="inlineStr">
+      <c r="I40" s="12" t="inlineStr">
         <is>
           <t>Lanzado</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="24" customHeight="1">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="41" ht="24" customHeight="1">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>Fase 5: Resultados</t>
         </is>
       </c>
-      <c r="B40" s="3" t="n"/>
-      <c r="C40" s="3" t="n"/>
-      <c r="D40" s="3" t="n"/>
-      <c r="E40" s="3" t="n"/>
-      <c r="F40" s="3" t="n"/>
-      <c r="G40" s="3" t="n"/>
-      <c r="H40" s="3" t="n"/>
-      <c r="I40" s="3" t="n"/>
-    </row>
-    <row r="41" ht="24" customHeight="1">
-      <c r="A41" s="4" t="n"/>
-      <c r="B41" s="5" t="n">
-        <v>26</v>
-      </c>
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t>Pruebas de analisis con URLs reales</t>
-        </is>
-      </c>
-      <c r="D41" s="6" t="inlineStr">
-        <is>
-          <t>Marco</t>
-        </is>
-      </c>
-      <c r="E41" s="7" t="n">
-        <v>46173</v>
-      </c>
-      <c r="F41" s="7" t="n">
-        <v>46189</v>
-      </c>
-      <c r="G41" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="H41" s="5" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="I41" s="14" t="inlineStr">
-        <is>
-          <t>En Progreso</t>
-        </is>
-      </c>
+      <c r="B41" s="3" t="n"/>
+      <c r="C41" s="3" t="n"/>
+      <c r="D41" s="3" t="n"/>
+      <c r="E41" s="3" t="n"/>
+      <c r="F41" s="3" t="n"/>
+      <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
+      <c r="I41" s="3" t="n"/>
     </row>
     <row r="42" ht="24" customHeight="1">
       <c r="A42" s="4" t="n"/>
       <c r="B42" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>Pruebas de analisis con URLs reales (positivas, negativas, estafas, satira)</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>Marco</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="n">
+        <v>46139</v>
+      </c>
+      <c r="F42" s="7" t="n">
+        <v>46153</v>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="H42" s="5" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="I42" s="14" t="inlineStr">
+        <is>
+          <t>En Progreso</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="24" customHeight="1">
+      <c r="A43" s="4" t="n"/>
+      <c r="B43" s="5" t="n">
         <v>27</v>
       </c>
-      <c r="C42" s="4" t="inlineStr">
-        <is>
-          <t>Evaluacion de precision del clasificador</t>
-        </is>
-      </c>
-      <c r="D42" s="6" t="inlineStr">
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>Correccion de errores: timeouts (AbortController 60s), override de dominios confiables, edge cases</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
         <is>
           <t>Marco</t>
         </is>
       </c>
-      <c r="E42" s="7" t="n">
-        <v>46190</v>
-      </c>
-      <c r="F42" s="7" t="n">
-        <v>46206</v>
-      </c>
-      <c r="G42" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="H42" s="5" t="inlineStr">
+      <c r="E43" s="7" t="n">
+        <v>46154</v>
+      </c>
+      <c r="F43" s="7" t="n">
+        <v>46166</v>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="I42" s="14" t="inlineStr">
+      <c r="I43" s="14" t="inlineStr">
         <is>
           <t>En Progreso</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="24" customHeight="1">
-      <c r="A43" s="11" t="n"/>
-      <c r="B43" s="12" t="inlineStr">
+    <row r="44" ht="24" customHeight="1">
+      <c r="A44" s="11" t="n"/>
+      <c r="B44" s="12" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="C43" s="11" t="inlineStr">
-        <is>
-          <t>v1.1.0 - Refinamiento y optimizacion del clasificador</t>
-        </is>
-      </c>
-      <c r="D43" s="12" t="inlineStr">
+      <c r="C44" s="11" t="inlineStr">
+        <is>
+          <t>v1.1.0 - Refinamiento y correccion de errores del clasificador</t>
+        </is>
+      </c>
+      <c r="D44" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E43" s="13" t="n">
-        <v>46207</v>
-      </c>
-      <c r="F43" s="13" t="n">
-        <v>46208</v>
-      </c>
-      <c r="G43" s="12" t="n">
+      <c r="E44" s="13" t="n">
+        <v>46167</v>
+      </c>
+      <c r="F44" s="13" t="n">
+        <v>46168</v>
+      </c>
+      <c r="G44" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H43" s="12" t="inlineStr">
+      <c r="H44" s="12" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="I43" s="12" t="inlineStr">
+      <c r="I44" s="12" t="inlineStr">
         <is>
           <t>Lanzado</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="24" customHeight="1">
-      <c r="A44" s="4" t="n"/>
-      <c r="B44" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="C44" s="4" t="inlineStr">
-        <is>
-          <t>Analisis de casos de prueba</t>
-        </is>
-      </c>
-      <c r="D44" s="9" t="inlineStr">
-        <is>
-          <t>Tony</t>
-        </is>
-      </c>
-      <c r="E44" s="7" t="n">
-        <v>46207</v>
-      </c>
-      <c r="F44" s="7" t="n">
-        <v>46223</v>
-      </c>
-      <c r="G44" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="H44" s="5" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="I44" s="15" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
         </is>
       </c>
     </row>
     <row r="45" ht="24" customHeight="1">
       <c r="A45" s="4" t="n"/>
       <c r="B45" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>Analisis de casos de prueba y documentacion de resultados en tesis</t>
+        </is>
+      </c>
+      <c r="D45" s="9" t="inlineStr">
+        <is>
+          <t>Tony</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="n">
+        <v>46167</v>
+      </c>
+      <c r="F45" s="7" t="n">
+        <v>46183</v>
+      </c>
+      <c r="G45" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="I45" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="24" customHeight="1">
+      <c r="A46" s="4" t="n"/>
+      <c r="B46" s="5" t="n">
         <v>29</v>
       </c>
-      <c r="C45" s="4" t="inlineStr">
-        <is>
-          <t>Redaccion de resultados</t>
-        </is>
-      </c>
-      <c r="D45" s="16" t="inlineStr">
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>Redaccion de resultados, generacion de Gantt y version final de tesis</t>
+        </is>
+      </c>
+      <c r="D46" s="16" t="inlineStr">
         <is>
           <t>Ulises</t>
         </is>
       </c>
-      <c r="E45" s="7" t="n">
-        <v>46224</v>
-      </c>
-      <c r="F45" s="7" t="n">
-        <v>46248</v>
-      </c>
-      <c r="G45" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="H45" s="5" t="inlineStr">
+      <c r="E46" s="7" t="n">
+        <v>46184</v>
+      </c>
+      <c r="F46" s="7" t="n">
+        <v>46202</v>
+      </c>
+      <c r="G46" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="H46" s="5" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="I45" s="15" t="inlineStr">
+      <c r="I46" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="24" customHeight="1">
-      <c r="A46" s="11" t="n"/>
-      <c r="B46" s="12" t="inlineStr">
+    <row r="47" ht="24" customHeight="1">
+      <c r="A47" s="11" t="n"/>
+      <c r="B47" s="12" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="C46" s="11" t="inlineStr">
-        <is>
-          <t>v1.2.0 - Version final de tesis con todas las funcionalidades</t>
-        </is>
-      </c>
-      <c r="D46" s="12" t="inlineStr">
+      <c r="C47" s="11" t="inlineStr">
+        <is>
+          <t>v1.2.0 - Version final de tesis con todas las funcionalidades implementadas y documentadas</t>
+        </is>
+      </c>
+      <c r="D47" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E46" s="13" t="n">
-        <v>46249</v>
-      </c>
-      <c r="F46" s="13" t="n">
-        <v>46250</v>
-      </c>
-      <c r="G46" s="12" t="n">
+      <c r="E47" s="13" t="n">
+        <v>46203</v>
+      </c>
+      <c r="F47" s="13" t="n">
+        <v>46204</v>
+      </c>
+      <c r="G47" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H46" s="12" t="inlineStr">
+      <c r="H47" s="12" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="I46" s="12" t="inlineStr">
+      <c r="I47" s="12" t="inlineStr">
         <is>
           <t>Lanzado</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="24" customHeight="1"/>
     <row r="48" ht="24" customHeight="1"/>
-    <row r="49" ht="24" customHeight="1">
-      <c r="A49" s="17" t="inlineStr">
+    <row r="49" ht="24" customHeight="1"/>
+    <row r="50" ht="24" customHeight="1">
+      <c r="A50" s="17" t="inlineStr">
         <is>
           <t>Leyenda:</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="24" customHeight="1">
-      <c r="A50" s="18" t="inlineStr">
-        <is>
-          <t>Marco - Programacion (backend, frontend, IA, deploy)</t>
-        </is>
-      </c>
-      <c r="B50" s="19" t="n"/>
-      <c r="C50" s="19" t="n"/>
-      <c r="D50" s="19" t="n"/>
-    </row>
     <row r="51" ht="24" customHeight="1">
-      <c r="A51" s="20" t="inlineStr">
-        <is>
-          <t>Luis - Frontend, diseno UI/UX y documentacion</t>
-        </is>
-      </c>
-      <c r="B51" s="21" t="n"/>
-      <c r="C51" s="21" t="n"/>
-      <c r="D51" s="21" t="n"/>
+      <c r="A51" s="18" t="inlineStr">
+        <is>
+          <t>Marco - Backend, frontend, IA, deploy y pruebas</t>
+        </is>
+      </c>
+      <c r="B51" s="19" t="n"/>
+      <c r="C51" s="19" t="n"/>
+      <c r="D51" s="19" t="n"/>
     </row>
     <row r="52" ht="24" customHeight="1">
-      <c r="A52" s="22" t="inlineStr">
-        <is>
-          <t>Ulises - Documentacion (redaccion de tesis)</t>
-        </is>
-      </c>
-      <c r="B52" s="23" t="n"/>
-      <c r="C52" s="23" t="n"/>
-      <c r="D52" s="23" t="n"/>
+      <c r="A52" s="20" t="inlineStr">
+        <is>
+          <t>Luis - Frontend, diseno UI/UX y estilos visuales</t>
+        </is>
+      </c>
+      <c r="B52" s="21" t="n"/>
+      <c r="C52" s="21" t="n"/>
+      <c r="D52" s="21" t="n"/>
     </row>
     <row r="53" ht="24" customHeight="1">
-      <c r="A53" s="24" t="inlineStr">
-        <is>
-          <t>Tony - Documentacion, metodologia y revision de logica</t>
-        </is>
-      </c>
-      <c r="B53" s="25" t="n"/>
-      <c r="C53" s="25" t="n"/>
-      <c r="D53" s="25" t="n"/>
+      <c r="A53" s="22" t="inlineStr">
+        <is>
+          <t>Ulises - Documentacion y redaccion de tesis</t>
+        </is>
+      </c>
+      <c r="B53" s="23" t="n"/>
+      <c r="C53" s="23" t="n"/>
+      <c r="D53" s="23" t="n"/>
     </row>
     <row r="54" ht="24" customHeight="1">
-      <c r="A54" s="26" t="inlineStr">
+      <c r="A54" s="24" t="inlineStr">
+        <is>
+          <t>Tony - Diagramas UML, documentacion y revision de logica</t>
+        </is>
+      </c>
+      <c r="B54" s="25" t="n"/>
+      <c r="C54" s="25" t="n"/>
+      <c r="D54" s="25" t="n"/>
+    </row>
+    <row r="55" ht="24" customHeight="1">
+      <c r="A55" s="26" t="inlineStr">
         <is>
           <t>★ Version - Hito de lanzamiento de version</t>
         </is>
       </c>
-      <c r="B54" s="27" t="n"/>
-      <c r="C54" s="27" t="n"/>
-      <c r="D54" s="27" t="n"/>
+      <c r="B55" s="27" t="n"/>
+      <c r="C55" s="27" t="n"/>
+      <c r="D55" s="27" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I47"/>
+  <autoFilter ref="A1:I48"/>
   <mergeCells count="10">
-    <mergeCell ref="A7:I7"/>
-    <mergeCell ref="A33:I33"/>
+    <mergeCell ref="A41:I41"/>
     <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A11:I11"/>
+    <mergeCell ref="A10:I10"/>
     <mergeCell ref="A53:D53"/>
-    <mergeCell ref="A50:D50"/>
     <mergeCell ref="A54:D54"/>
-    <mergeCell ref="A40:I40"/>
+    <mergeCell ref="A55:D55"/>
     <mergeCell ref="A52:D52"/>
+    <mergeCell ref="A6:I6"/>
     <mergeCell ref="A51:D51"/>
+    <mergeCell ref="A34:I34"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>

--- a/Gantt_VERIFEX.xlsx
+++ b/Gantt_VERIFEX.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gantt VERIFEX" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Gantt VERIFEX'!$A$1:$J$75</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Gantt VERIFEX'!$A$1:$J$116</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -22,7 +22,7 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="DD/MM/YYYY"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -67,19 +67,7 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="001B5E20"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
       <color rgb="004A148C"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00B71C1C"/>
       <sz val="10"/>
     </font>
     <font>
@@ -91,19 +79,13 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00E65100"/>
+      <color rgb="001B5E20"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00F57F17"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00C62828"/>
+      <color rgb="00E65100"/>
       <sz val="10"/>
     </font>
     <font>
@@ -112,7 +94,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -153,12 +135,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F3E5F5"/>
         <bgColor rgb="00F3E5F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFEBEE"/>
-        <bgColor rgb="00FFEBEE"/>
       </patternFill>
     </fill>
     <fill>
@@ -244,7 +220,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -275,44 +251,33 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="10" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -678,7 +643,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J84"/>
+  <dimension ref="A1:J125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -801,10 +766,10 @@
         <v>45901</v>
       </c>
       <c r="G4" s="10" t="n">
-        <v>45908</v>
+        <v>45910</v>
       </c>
       <c r="H4" s="8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I4" s="8" t="n"/>
       <c r="J4" s="11" t="inlineStr">
@@ -834,13 +799,13 @@
         </is>
       </c>
       <c r="F5" s="10" t="n">
-        <v>45909</v>
+        <v>45911</v>
       </c>
       <c r="G5" s="10" t="n">
-        <v>45923</v>
+        <v>45933</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="I5" s="8" t="inlineStr">
         <is>
@@ -868,16 +833,16 @@
           <t>Definicion del problema, preguntas de investigacion y objetivos</t>
         </is>
       </c>
-      <c r="E6" s="12" t="inlineStr">
-        <is>
-          <t>Ulises</t>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>Todos</t>
         </is>
       </c>
       <c r="F6" s="10" t="n">
-        <v>45924</v>
+        <v>45934</v>
       </c>
       <c r="G6" s="10" t="n">
-        <v>45929</v>
+        <v>45939</v>
       </c>
       <c r="H6" s="8" t="n">
         <v>6</v>
@@ -905,145 +870,145 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>Seleccion de tecnologias: Groq API vs Ollama, React vs Vue, Flask vs FastAPI</t>
-        </is>
-      </c>
-      <c r="E7" s="13" t="inlineStr">
+          <t>Aprobacion formal del tema de tesis y delimitacion del alcance</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+      <c r="F7" s="10" t="n">
+        <v>45940</v>
+      </c>
+      <c r="G7" s="10" t="n">
+        <v>45943</v>
+      </c>
+      <c r="H7" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="I7" s="8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" s="11" t="inlineStr">
+        <is>
+          <t>Completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Ciclo 1: Fundamentos Teoricos y Requisitos</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n"/>
+      <c r="C8" s="3" t="n"/>
+      <c r="D8" s="3" t="n"/>
+      <c r="E8" s="3" t="n"/>
+      <c r="F8" s="3" t="n"/>
+      <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
+      <c r="I8" s="3" t="n"/>
+      <c r="J8" s="3" t="n"/>
+    </row>
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Fase 1: Marco Teorico e Historias de Usuario</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n"/>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="5" t="n"/>
+      <c r="I9" s="5" t="n"/>
+      <c r="J9" s="5" t="n"/>
+    </row>
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="6" t="n"/>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>Backend e IA: Groq API, Flask, scraping, curl_cffi, Playwright</t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="inlineStr">
         <is>
           <t>Marco</t>
         </is>
       </c>
-      <c r="F7" s="10" t="n">
-        <v>45930</v>
-      </c>
-      <c r="G7" s="10" t="n">
-        <v>45935</v>
-      </c>
-      <c r="H7" s="8" t="n">
+      <c r="F10" s="10" t="n">
+        <v>45944</v>
+      </c>
+      <c r="G10" s="10" t="n">
+        <v>45962</v>
+      </c>
+      <c r="H10" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="I10" s="8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J10" s="11" t="inlineStr">
+        <is>
+          <t>Completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="24" customHeight="1">
+      <c r="A11" s="6" t="n"/>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="I7" s="8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J7" s="11" t="inlineStr">
-        <is>
-          <t>Completado</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="6" t="n"/>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>Sprint</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>Justificacion del proyecto y delimitacion del alcance</t>
-        </is>
-      </c>
-      <c r="E8" s="12" t="inlineStr">
-        <is>
-          <t>Ulises</t>
-        </is>
-      </c>
-      <c r="F8" s="10" t="n">
-        <v>45936</v>
-      </c>
-      <c r="G8" s="10" t="n">
-        <v>45941</v>
-      </c>
-      <c r="H8" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="I8" s="8" t="inlineStr">
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>UI/UX cyberpunk: React, Tailwind, tipografia, paletas</t>
+        </is>
+      </c>
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>Luis</t>
+        </is>
+      </c>
+      <c r="F11" s="10" t="n">
+        <v>45944</v>
+      </c>
+      <c r="G11" s="10" t="n">
+        <v>45961</v>
+      </c>
+      <c r="H11" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="I11" s="8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J8" s="11" t="inlineStr">
-        <is>
-          <t>Completado</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="6" t="n"/>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>Sprint</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>Aprobacion formal del tema de tesis</t>
-        </is>
-      </c>
-      <c r="E9" s="9" t="inlineStr">
-        <is>
-          <t>Todos</t>
-        </is>
-      </c>
-      <c r="F9" s="10" t="n">
-        <v>45942</v>
-      </c>
-      <c r="G9" s="10" t="n">
-        <v>45945</v>
-      </c>
-      <c r="H9" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="I9" s="8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J9" s="11" t="inlineStr">
-        <is>
-          <t>Completado</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Ciclo 1: Fundamentos Teoricos y Requisitos</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="n"/>
-      <c r="C10" s="3" t="n"/>
-      <c r="D10" s="3" t="n"/>
-      <c r="E10" s="3" t="n"/>
-      <c r="F10" s="3" t="n"/>
-      <c r="G10" s="3" t="n"/>
-      <c r="H10" s="3" t="n"/>
-      <c r="I10" s="3" t="n"/>
-      <c r="J10" s="3" t="n"/>
-    </row>
-    <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>Fase 1: Marco Teorico e Historias de Usuario</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="n"/>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
-      <c r="G11" s="5" t="n"/>
-      <c r="H11" s="5" t="n"/>
-      <c r="I11" s="5" t="n"/>
-      <c r="J11" s="5" t="n"/>
+      <c r="J11" s="11" t="inlineStr">
+        <is>
+          <t>Completado</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="24" customHeight="1">
       <c r="A12" s="6" t="n"/>
@@ -1057,26 +1022,26 @@
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>Redaccion del Capitulo 1: Introduccion (contexto, problema, objetivos, justificacion)</t>
-        </is>
-      </c>
-      <c r="E12" s="12" t="inlineStr">
+          <t>Marco teorico: fake news, verificacion digital, desinformacion MX</t>
+        </is>
+      </c>
+      <c r="E12" s="14" t="inlineStr">
         <is>
           <t>Ulises</t>
         </is>
       </c>
       <c r="F12" s="10" t="n">
-        <v>45946</v>
+        <v>45944</v>
       </c>
       <c r="G12" s="10" t="n">
-        <v>45958</v>
+        <v>45963</v>
       </c>
       <c r="H12" s="8" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="I12" s="8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J12" s="11" t="inlineStr">
@@ -1097,26 +1062,26 @@
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>Definicion de 10 historias de usuario (HU-01 a HU-10)</t>
-        </is>
-      </c>
-      <c r="E13" s="13" t="inlineStr">
+          <t>Herramientas de prueba: Vitest, Pytest, Playwright, Selenium</t>
+        </is>
+      </c>
+      <c r="E13" s="12" t="inlineStr">
         <is>
           <t>Marco</t>
         </is>
       </c>
       <c r="F13" s="10" t="n">
-        <v>45959</v>
+        <v>45944</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>45969</v>
+        <v>45962</v>
       </c>
       <c r="H13" s="8" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="I13" s="8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J13" s="11" t="inlineStr">
@@ -1137,26 +1102,26 @@
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>Investigacion sobre IA, Groq API, procesamiento de lenguaje natural</t>
-        </is>
-      </c>
-      <c r="E14" s="13" t="inlineStr">
+          <t>Seleccion de tecnologias y definicion de requisitos funcionales</t>
+        </is>
+      </c>
+      <c r="E14" s="12" t="inlineStr">
         <is>
           <t>Marco</t>
         </is>
       </c>
       <c r="F14" s="10" t="n">
-        <v>45970</v>
+        <v>45963</v>
       </c>
       <c r="G14" s="10" t="n">
-        <v>45978</v>
+        <v>45975</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I14" s="8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J14" s="11" t="inlineStr">
@@ -1177,26 +1142,26 @@
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>Redaccion del Capitulo 2: Marco Teorico (fake news, IA, Groq API, verificacion)</t>
-        </is>
-      </c>
-      <c r="E15" s="12" t="inlineStr">
-        <is>
-          <t>Ulises</t>
+          <t>Historias de usuario (HU-01 a HU-10) y diseno conceptual de interfaz</t>
+        </is>
+      </c>
+      <c r="E15" s="13" t="inlineStr">
+        <is>
+          <t>Luis</t>
         </is>
       </c>
       <c r="F15" s="10" t="n">
-        <v>45979</v>
+        <v>45962</v>
       </c>
       <c r="G15" s="10" t="n">
-        <v>45993</v>
+        <v>45973</v>
       </c>
       <c r="H15" s="8" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I15" s="8" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J15" s="11" t="inlineStr">
@@ -1217,26 +1182,26 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>Definicion de requisitos funcionales y no funcionales</t>
-        </is>
-      </c>
-      <c r="E16" s="13" t="inlineStr">
-        <is>
-          <t>Marco</t>
+          <t>Planteamiento del problema, justificacion y preguntas de investigacion</t>
+        </is>
+      </c>
+      <c r="E16" s="14" t="inlineStr">
+        <is>
+          <t>Ulises</t>
         </is>
       </c>
       <c r="F16" s="10" t="n">
-        <v>45994</v>
+        <v>45964</v>
       </c>
       <c r="G16" s="10" t="n">
-        <v>46002</v>
+        <v>45977</v>
       </c>
       <c r="H16" s="8" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="I16" s="8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J16" s="11" t="inlineStr">
@@ -1257,26 +1222,26 @@
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>Creacion de diagramas UML (casos de uso, actividades, secuencia, clases, ER)</t>
+          <t>Metricas de calidad, criterios de aceptacion y matriz de trazabilidad</t>
         </is>
       </c>
       <c r="E17" s="14" t="inlineStr">
         <is>
-          <t>Tony</t>
+          <t>Ulises</t>
         </is>
       </c>
       <c r="F17" s="10" t="n">
-        <v>46003</v>
+        <v>45963</v>
       </c>
       <c r="G17" s="10" t="n">
-        <v>46015</v>
+        <v>45975</v>
       </c>
       <c r="H17" s="8" t="n">
         <v>13</v>
       </c>
       <c r="I17" s="8" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J17" s="11" t="inlineStr">
@@ -1286,36 +1251,84 @@
       </c>
     </row>
     <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>Ciclo 2: Diseno del Sistema</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="n"/>
-      <c r="C18" s="3" t="n"/>
-      <c r="D18" s="3" t="n"/>
-      <c r="E18" s="3" t="n"/>
-      <c r="F18" s="3" t="n"/>
-      <c r="G18" s="3" t="n"/>
-      <c r="H18" s="3" t="n"/>
-      <c r="I18" s="3" t="n"/>
-      <c r="J18" s="3" t="n"/>
+      <c r="A18" s="6" t="n"/>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>Setup de entorno: Node, Python, Git, VSCode, dependencias</t>
+        </is>
+      </c>
+      <c r="E18" s="12" t="inlineStr">
+        <is>
+          <t>Marco</t>
+        </is>
+      </c>
+      <c r="F18" s="10" t="n">
+        <v>45976</v>
+      </c>
+      <c r="G18" s="10" t="n">
+        <v>45986</v>
+      </c>
+      <c r="H18" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="I18" s="8" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J18" s="11" t="inlineStr">
+        <is>
+          <t>Completado</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>Fase 2: Diseno y Metodologia</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="n"/>
-      <c r="C19" s="5" t="n"/>
-      <c r="D19" s="5" t="n"/>
-      <c r="E19" s="5" t="n"/>
-      <c r="F19" s="5" t="n"/>
-      <c r="G19" s="5" t="n"/>
-      <c r="H19" s="5" t="n"/>
-      <c r="I19" s="5" t="n"/>
-      <c r="J19" s="5" t="n"/>
+      <c r="A19" s="6" t="n"/>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>Moodboard, exploracion de componentes UI y paleta de colores</t>
+        </is>
+      </c>
+      <c r="E19" s="13" t="inlineStr">
+        <is>
+          <t>Luis</t>
+        </is>
+      </c>
+      <c r="F19" s="10" t="n">
+        <v>45974</v>
+      </c>
+      <c r="G19" s="10" t="n">
+        <v>45983</v>
+      </c>
+      <c r="H19" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="I19" s="8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J19" s="11" t="inlineStr">
+        <is>
+          <t>Completado</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="24" customHeight="1">
       <c r="A20" s="6" t="n"/>
@@ -1325,30 +1338,30 @@
         </is>
       </c>
       <c r="C20" s="8" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>Redaccion del Capitulo 3: Metodologia y Diseno del Sistema (inicio)</t>
-        </is>
-      </c>
-      <c r="E20" s="12" t="inlineStr">
+          <t>Capitulo 1: Introduccion (contexto, problema, objetivos, alcance)</t>
+        </is>
+      </c>
+      <c r="E20" s="14" t="inlineStr">
         <is>
           <t>Ulises</t>
         </is>
       </c>
       <c r="F20" s="10" t="n">
-        <v>46016</v>
+        <v>45978</v>
       </c>
       <c r="G20" s="10" t="n">
-        <v>46024</v>
+        <v>45989</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I20" s="8" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J20" s="11" t="inlineStr">
@@ -1365,30 +1378,30 @@
         </is>
       </c>
       <c r="C21" s="8" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>Diseno de wireframes y mockups de interfaz de usuario</t>
-        </is>
-      </c>
-      <c r="E21" s="15" t="inlineStr">
-        <is>
-          <t>Luis</t>
+          <t>Plan maestro de pruebas y diseno de casos de prueba iniciales</t>
+        </is>
+      </c>
+      <c r="E21" s="14" t="inlineStr">
+        <is>
+          <t>Ulises</t>
         </is>
       </c>
       <c r="F21" s="10" t="n">
-        <v>46025</v>
+        <v>45976</v>
       </c>
       <c r="G21" s="10" t="n">
-        <v>46035</v>
+        <v>45986</v>
       </c>
       <c r="H21" s="8" t="n">
         <v>11</v>
       </c>
       <c r="I21" s="8" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J21" s="11" t="inlineStr">
@@ -1405,30 +1418,30 @@
         </is>
       </c>
       <c r="C22" s="8" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>Seleccion de paleta de colores y fuentes (Orbitron, Rajdhani, Share Tech Mono)</t>
-        </is>
-      </c>
-      <c r="E22" s="15" t="inlineStr">
-        <is>
-          <t>Luis</t>
+          <t>Revision consolidacion: requisitos, HU y plan de pruebas</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>Todos</t>
         </is>
       </c>
       <c r="F22" s="10" t="n">
-        <v>46036</v>
+        <v>45987</v>
       </c>
       <c r="G22" s="10" t="n">
-        <v>46041</v>
+        <v>45994</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I22" s="8" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J22" s="11" t="inlineStr">
@@ -1438,42 +1451,44 @@
       </c>
     </row>
     <row r="23" ht="24" customHeight="1">
-      <c r="A23" s="6" t="n"/>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>Sprint</t>
-        </is>
-      </c>
-      <c r="C23" s="8" t="n">
-        <v>16</v>
-      </c>
-      <c r="D23" s="6" t="inlineStr">
-        <is>
-          <t>Diseno de arquitectura cliente-servidor (React + Flask + Groq API)</t>
-        </is>
-      </c>
-      <c r="E23" s="13" t="inlineStr">
-        <is>
-          <t>Marco</t>
-        </is>
-      </c>
-      <c r="F23" s="10" t="n">
-        <v>46042</v>
-      </c>
-      <c r="G23" s="10" t="n">
-        <v>46050</v>
-      </c>
-      <c r="H23" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I23" s="8" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J23" s="11" t="inlineStr">
-        <is>
-          <t>Completado</t>
+      <c r="A23" s="15" t="n"/>
+      <c r="B23" s="16" t="inlineStr">
+        <is>
+          <t>Iteracion</t>
+        </is>
+      </c>
+      <c r="C23" s="16" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="D23" s="15" t="inlineStr">
+        <is>
+          <t>v0.1.0 - Requisitos, HU, marco teorico y plan de pruebas definidos</t>
+        </is>
+      </c>
+      <c r="E23" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="17" t="n">
+        <v>45995</v>
+      </c>
+      <c r="G23" s="17" t="n">
+        <v>45996</v>
+      </c>
+      <c r="H23" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="I23" s="16" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J23" s="16" t="inlineStr">
+        <is>
+          <t>Lanzado</t>
         </is>
       </c>
     </row>
@@ -1485,30 +1500,30 @@
         </is>
       </c>
       <c r="C24" s="8" t="n">
-        <v>17</v>
+        <v>86</v>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>Redaccion del Capitulo 3: Finalizacion (arquitectura, componentes, flujo)</t>
-        </is>
-      </c>
-      <c r="E24" s="12" t="inlineStr">
-        <is>
-          <t>Ulises</t>
+          <t>Revision y retroalimentacion del Ciclo 1: ajustes a requisitos, HU y marco teorico</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t>Todos</t>
         </is>
       </c>
       <c r="F24" s="10" t="n">
-        <v>46051</v>
+        <v>45995</v>
       </c>
       <c r="G24" s="10" t="n">
-        <v>46057</v>
+        <v>46000</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I24" s="8" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J24" s="11" t="inlineStr">
@@ -1520,7 +1535,7 @@
     <row r="25" ht="24" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Ciclo 3: Desarrollo del Sistema</t>
+          <t>Ciclo 2: Diseno del Sistema</t>
         </is>
       </c>
       <c r="B25" s="3" t="n"/>
@@ -1536,7 +1551,7 @@
     <row r="26" ht="24" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>Fase 3: Implementacion</t>
+          <t>Fase 2: Diseno del Sistema</t>
         </is>
       </c>
       <c r="B26" s="5" t="n"/>
@@ -1561,26 +1576,26 @@
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>Setup del proyecto (Vite + React + TypeScript + Tailwind + PostCSS)</t>
-        </is>
-      </c>
-      <c r="E27" s="13" t="inlineStr">
+          <t>Arquitectura cliente-servidor: React + Flask + Groq API + Playwright + CORS</t>
+        </is>
+      </c>
+      <c r="E27" s="12" t="inlineStr">
         <is>
           <t>Marco</t>
         </is>
       </c>
       <c r="F27" s="10" t="n">
-        <v>46058</v>
+        <v>46001</v>
       </c>
       <c r="G27" s="10" t="n">
-        <v>46063</v>
+        <v>46013</v>
       </c>
       <c r="H27" s="8" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="I27" s="8" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>86</t>
         </is>
       </c>
       <c r="J27" s="11" t="inlineStr">
@@ -1590,44 +1605,42 @@
       </c>
     </row>
     <row r="28" ht="24" customHeight="1">
-      <c r="A28" s="16" t="n"/>
-      <c r="B28" s="17" t="inlineStr">
-        <is>
-          <t>Iteracion</t>
-        </is>
-      </c>
-      <c r="C28" s="17" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="D28" s="16" t="inlineStr">
-        <is>
-          <t>v0.0.1 - Esqueleto del proyecto con Vite, React, TypeScript y Tailwind configurados</t>
-        </is>
-      </c>
-      <c r="E28" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F28" s="18" t="n">
-        <v>46064</v>
-      </c>
-      <c r="G28" s="18" t="n">
-        <v>46065</v>
-      </c>
-      <c r="H28" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="I28" s="17" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J28" s="17" t="inlineStr">
-        <is>
-          <t>Lanzado</t>
+      <c r="A28" s="6" t="n"/>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>Wireframes baja fidelidad y prototipo navegable alta fidelidad</t>
+        </is>
+      </c>
+      <c r="E28" s="13" t="inlineStr">
+        <is>
+          <t>Luis</t>
+        </is>
+      </c>
+      <c r="F28" s="10" t="n">
+        <v>46001</v>
+      </c>
+      <c r="G28" s="10" t="n">
+        <v>46012</v>
+      </c>
+      <c r="H28" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I28" s="8" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="J28" s="11" t="inlineStr">
+        <is>
+          <t>Completado</t>
         </is>
       </c>
     </row>
@@ -1639,30 +1652,30 @@
         </is>
       </c>
       <c r="C29" s="8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>Setup del backend (Flask + CORS + rutas /analyze y /health)</t>
-        </is>
-      </c>
-      <c r="E29" s="13" t="inlineStr">
-        <is>
-          <t>Marco</t>
+          <t>Capitulo 2: Marco Teorico (fake news, IA, Groq API, verificacion)</t>
+        </is>
+      </c>
+      <c r="E29" s="14" t="inlineStr">
+        <is>
+          <t>Ulises</t>
         </is>
       </c>
       <c r="F29" s="10" t="n">
-        <v>46064</v>
+        <v>46001</v>
       </c>
       <c r="G29" s="10" t="n">
-        <v>46069</v>
+        <v>46014</v>
       </c>
       <c r="H29" s="8" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I29" s="8" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>86</t>
         </is>
       </c>
       <c r="J29" s="11" t="inlineStr">
@@ -1679,77 +1692,75 @@
         </is>
       </c>
       <c r="C30" s="8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>Implementacion del scraper de URLs con BeautifulSoup (scrape_url)</t>
+          <t>Diagramas UML: casos de uso, actividades, secuencia, clases, ER</t>
         </is>
       </c>
       <c r="E30" s="13" t="inlineStr">
         <is>
+          <t>Luis</t>
+        </is>
+      </c>
+      <c r="F30" s="10" t="n">
+        <v>46001</v>
+      </c>
+      <c r="G30" s="10" t="n">
+        <v>46013</v>
+      </c>
+      <c r="H30" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="I30" s="8" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="J30" s="11" t="inlineStr">
+        <is>
+          <t>Completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="24" customHeight="1">
+      <c r="A31" s="6" t="n"/>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>Setup proyecto: Vite + React + TypeScript + Tailwind + PostCSS</t>
+        </is>
+      </c>
+      <c r="E31" s="12" t="inlineStr">
+        <is>
           <t>Marco</t>
         </is>
       </c>
-      <c r="F30" s="10" t="n">
-        <v>46070</v>
-      </c>
-      <c r="G30" s="10" t="n">
-        <v>46080</v>
-      </c>
-      <c r="H30" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="I30" s="8" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="J30" s="11" t="inlineStr">
-        <is>
-          <t>Completado</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="24" customHeight="1">
-      <c r="A31" s="16" t="n"/>
-      <c r="B31" s="17" t="inlineStr">
-        <is>
-          <t>Iteracion</t>
-        </is>
-      </c>
-      <c r="C31" s="17" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="D31" s="16" t="inlineStr">
-        <is>
-          <t>v0.1.0 - Scraper de URLs funcional (extrae titulo, descripcion y cuerpo)</t>
-        </is>
-      </c>
-      <c r="E31" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F31" s="18" t="n">
-        <v>46081</v>
-      </c>
-      <c r="G31" s="18" t="n">
-        <v>46082</v>
-      </c>
-      <c r="H31" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="I31" s="17" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J31" s="17" t="inlineStr">
-        <is>
-          <t>Lanzado</t>
+      <c r="F31" s="10" t="n">
+        <v>46014</v>
+      </c>
+      <c r="G31" s="10" t="n">
+        <v>46022</v>
+      </c>
+      <c r="H31" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="I31" s="8" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J31" s="11" t="inlineStr">
+        <is>
+          <t>Completado</t>
         </is>
       </c>
     </row>
@@ -1761,30 +1772,30 @@
         </is>
       </c>
       <c r="C32" s="8" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>Integracion con Groq API (call_groq con fallback a multiples modelos)</t>
+          <t>Paleta colores definitiva, tipografia (Orbitron, Rajdhani) y guia de estilos</t>
         </is>
       </c>
       <c r="E32" s="13" t="inlineStr">
         <is>
-          <t>Marco</t>
+          <t>Luis</t>
         </is>
       </c>
       <c r="F32" s="10" t="n">
-        <v>46081</v>
+        <v>46013</v>
       </c>
       <c r="G32" s="10" t="n">
-        <v>46091</v>
+        <v>46020</v>
       </c>
       <c r="H32" s="8" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I32" s="8" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J32" s="11" t="inlineStr">
@@ -1801,77 +1812,75 @@
         </is>
       </c>
       <c r="C33" s="8" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>Implementacion de prompt engineering (SYSTEM_PROMPT con clasificacion 5 categorias)</t>
-        </is>
-      </c>
-      <c r="E33" s="13" t="inlineStr">
+          <t>Diagrama Gantt y tablero Kanban (Gantt_VERIFEX.xlsx, Kanban_VERIFEX.xlsx)</t>
+        </is>
+      </c>
+      <c r="E33" s="14" t="inlineStr">
+        <is>
+          <t>Ulises</t>
+        </is>
+      </c>
+      <c r="F33" s="10" t="n">
+        <v>46015</v>
+      </c>
+      <c r="G33" s="10" t="n">
+        <v>46024</v>
+      </c>
+      <c r="H33" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="I33" s="8" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J33" s="11" t="inlineStr">
+        <is>
+          <t>Completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="24" customHeight="1">
+      <c r="A34" s="6" t="n"/>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>Datos de prueba y configuracion del entorno de validacion</t>
+        </is>
+      </c>
+      <c r="E34" s="12" t="inlineStr">
         <is>
           <t>Marco</t>
         </is>
       </c>
-      <c r="F33" s="10" t="n">
-        <v>46092</v>
-      </c>
-      <c r="G33" s="10" t="n">
-        <v>46100</v>
-      </c>
-      <c r="H33" s="8" t="n">
+      <c r="F34" s="10" t="n">
+        <v>46014</v>
+      </c>
+      <c r="G34" s="10" t="n">
+        <v>46022</v>
+      </c>
+      <c r="H34" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="I33" s="8" t="inlineStr">
+      <c r="I34" s="8" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="J33" s="11" t="inlineStr">
-        <is>
-          <t>Completado</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="24" customHeight="1">
-      <c r="A34" s="16" t="n"/>
-      <c r="B34" s="17" t="inlineStr">
-        <is>
-          <t>Iteracion</t>
-        </is>
-      </c>
-      <c r="C34" s="17" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="D34" s="16" t="inlineStr">
-        <is>
-          <t>v0.2.0 - Analisis con IA via Groq API implementado</t>
-        </is>
-      </c>
-      <c r="E34" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F34" s="18" t="n">
-        <v>46101</v>
-      </c>
-      <c r="G34" s="18" t="n">
-        <v>46102</v>
-      </c>
-      <c r="H34" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="I34" s="17" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J34" s="17" t="inlineStr">
-        <is>
-          <t>Lanzado</t>
+      <c r="J34" s="11" t="inlineStr">
+        <is>
+          <t>Completado</t>
         </is>
       </c>
     </row>
@@ -1883,26 +1892,26 @@
         </is>
       </c>
       <c r="C35" s="8" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>Implementacion del clasificador de credibilidad (analyze_url con 5 categorias)</t>
-        </is>
-      </c>
-      <c r="E35" s="13" t="inlineStr">
+          <t>Diseno detallado del scraper multi-estrategia y plan de extraccion</t>
+        </is>
+      </c>
+      <c r="E35" s="12" t="inlineStr">
         <is>
           <t>Marco</t>
         </is>
       </c>
       <c r="F35" s="10" t="n">
-        <v>46101</v>
+        <v>46023</v>
       </c>
       <c r="G35" s="10" t="n">
-        <v>46113</v>
+        <v>46033</v>
       </c>
       <c r="H35" s="8" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I35" s="8" t="inlineStr">
         <is>
@@ -1923,26 +1932,26 @@
         </is>
       </c>
       <c r="C36" s="8" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>Implementacion de lista de dominios confiables (CREDIBLE_DOMAINS, 29 fuentes)</t>
+          <t>Maquetacion: UrlInput, layout inicial y estructura de paneles</t>
         </is>
       </c>
       <c r="E36" s="13" t="inlineStr">
         <is>
-          <t>Marco</t>
+          <t>Luis</t>
         </is>
       </c>
       <c r="F36" s="10" t="n">
-        <v>46114</v>
+        <v>46021</v>
       </c>
       <c r="G36" s="10" t="n">
-        <v>46118</v>
+        <v>46030</v>
       </c>
       <c r="H36" s="8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I36" s="8" t="inlineStr">
         <is>
@@ -1956,44 +1965,42 @@
       </c>
     </row>
     <row r="37" ht="24" customHeight="1">
-      <c r="A37" s="16" t="n"/>
-      <c r="B37" s="17" t="inlineStr">
-        <is>
-          <t>Iteracion</t>
-        </is>
-      </c>
-      <c r="C37" s="17" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="D37" s="16" t="inlineStr">
-        <is>
-          <t>v0.3.0 - Clasificador de credibilidad funcional (REAL, FALSO, SATIRA, ESTAFA, NO VERIFICABLE)</t>
-        </is>
-      </c>
-      <c r="E37" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F37" s="18" t="n">
-        <v>46119</v>
-      </c>
-      <c r="G37" s="18" t="n">
-        <v>46120</v>
-      </c>
-      <c r="H37" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="I37" s="17" t="inlineStr">
+      <c r="A37" s="6" t="n"/>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="C37" s="8" t="n">
+        <v>28</v>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>Capitulo 3: Metodologia y Diseno del Sistema (arquitectura, metodos)</t>
+        </is>
+      </c>
+      <c r="E37" s="14" t="inlineStr">
+        <is>
+          <t>Ulises</t>
+        </is>
+      </c>
+      <c r="F37" s="10" t="n">
+        <v>46025</v>
+      </c>
+      <c r="G37" s="10" t="n">
+        <v>46036</v>
+      </c>
+      <c r="H37" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I37" s="8" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="J37" s="17" t="inlineStr">
-        <is>
-          <t>Lanzado</t>
+      <c r="J37" s="11" t="inlineStr">
+        <is>
+          <t>Completado</t>
         </is>
       </c>
     </row>
@@ -2005,239 +2012,189 @@
         </is>
       </c>
       <c r="C38" s="8" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>Busqueda de noticias similares via Google News RSS (news_finder.py)</t>
-        </is>
-      </c>
-      <c r="E38" s="13" t="inlineStr">
+          <t>Casos de prueba detallados para scraper y extraccion de contenido</t>
+        </is>
+      </c>
+      <c r="E38" s="12" t="inlineStr">
         <is>
           <t>Marco</t>
         </is>
       </c>
       <c r="F38" s="10" t="n">
-        <v>46119</v>
+        <v>46023</v>
       </c>
       <c r="G38" s="10" t="n">
-        <v>46127</v>
+        <v>46033</v>
       </c>
       <c r="H38" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="I38" s="8" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J38" s="11" t="inlineStr">
+        <is>
+          <t>Completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="24" customHeight="1">
+      <c r="A39" s="15" t="n"/>
+      <c r="B39" s="16" t="inlineStr">
+        <is>
+          <t>Iteracion</t>
+        </is>
+      </c>
+      <c r="C39" s="16" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="D39" s="15" t="inlineStr">
+        <is>
+          <t>v0.2.0 - Diseno completo: arquitectura, prototipo navegable, diagramas UML y plan de pruebas detallado</t>
+        </is>
+      </c>
+      <c r="E39" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F39" s="17" t="n">
+        <v>46034</v>
+      </c>
+      <c r="G39" s="17" t="n">
+        <v>46035</v>
+      </c>
+      <c r="H39" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="I39" s="16" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="J39" s="16" t="inlineStr">
+        <is>
+          <t>Lanzado</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="24" customHeight="1">
+      <c r="A40" s="6" t="n"/>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="C40" s="8" t="n">
+        <v>87</v>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>Revision y retroalimentacion del Ciclo 2: validacion de diseno, prototipo y plan de pruebas</t>
+        </is>
+      </c>
+      <c r="E40" s="9" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+      <c r="F40" s="10" t="n">
+        <v>46034</v>
+      </c>
+      <c r="G40" s="10" t="n">
+        <v>46039</v>
+      </c>
+      <c r="H40" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="I40" s="8" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="J40" s="11" t="inlineStr">
+        <is>
+          <t>Completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="24" customHeight="1">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Ciclo 3: Desarrollo del Sistema</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n"/>
+      <c r="C41" s="3" t="n"/>
+      <c r="D41" s="3" t="n"/>
+      <c r="E41" s="3" t="n"/>
+      <c r="F41" s="3" t="n"/>
+      <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
+      <c r="I41" s="3" t="n"/>
+      <c r="J41" s="3" t="n"/>
+    </row>
+    <row r="42" ht="24" customHeight="1">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Fase 3: Desarrollo del Sistema</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n"/>
+      <c r="C42" s="5" t="n"/>
+      <c r="D42" s="5" t="n"/>
+      <c r="E42" s="5" t="n"/>
+      <c r="F42" s="5" t="n"/>
+      <c r="G42" s="5" t="n"/>
+      <c r="H42" s="5" t="n"/>
+      <c r="I42" s="5" t="n"/>
+      <c r="J42" s="5" t="n"/>
+    </row>
+    <row r="43" ht="24" customHeight="1">
+      <c r="A43" s="6" t="n"/>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="C43" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>Setup Flask: rutas /analyze y /health, CORS, parse_response, errores</t>
+        </is>
+      </c>
+      <c r="E43" s="12" t="inlineStr">
+        <is>
+          <t>Marco</t>
+        </is>
+      </c>
+      <c r="F43" s="10" t="n">
+        <v>46040</v>
+      </c>
+      <c r="G43" s="10" t="n">
+        <v>46048</v>
+      </c>
+      <c r="H43" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="I38" s="8" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J38" s="11" t="inlineStr">
-        <is>
-          <t>Completado</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="24" customHeight="1">
-      <c r="A39" s="6" t="n"/>
-      <c r="B39" s="7" t="inlineStr">
-        <is>
-          <t>Sprint</t>
-        </is>
-      </c>
-      <c r="C39" s="8" t="n">
-        <v>26</v>
-      </c>
-      <c r="D39" s="6" t="inlineStr">
-        <is>
-          <t>Conexion frontend-backend via API REST (fetch /analyze con AbortController)</t>
-        </is>
-      </c>
-      <c r="E39" s="13" t="inlineStr">
-        <is>
-          <t>Marco</t>
-        </is>
-      </c>
-      <c r="F39" s="10" t="n">
-        <v>46128</v>
-      </c>
-      <c r="G39" s="10" t="n">
-        <v>46136</v>
-      </c>
-      <c r="H39" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I39" s="8" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J39" s="11" t="inlineStr">
-        <is>
-          <t>Completado</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="24" customHeight="1">
-      <c r="A40" s="16" t="n"/>
-      <c r="B40" s="17" t="inlineStr">
-        <is>
-          <t>Iteracion</t>
-        </is>
-      </c>
-      <c r="C40" s="17" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="D40" s="16" t="inlineStr">
-        <is>
-          <t>v0.4.0 - Frontend conectado al backend via API REST</t>
-        </is>
-      </c>
-      <c r="E40" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F40" s="18" t="n">
-        <v>46137</v>
-      </c>
-      <c r="G40" s="18" t="n">
-        <v>46138</v>
-      </c>
-      <c r="H40" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="I40" s="17" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="J40" s="17" t="inlineStr">
-        <is>
-          <t>Lanzado</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="24" customHeight="1">
-      <c r="A41" s="6" t="n"/>
-      <c r="B41" s="7" t="inlineStr">
-        <is>
-          <t>Sprint</t>
-        </is>
-      </c>
-      <c r="C41" s="8" t="n">
-        <v>27</v>
-      </c>
-      <c r="D41" s="6" t="inlineStr">
-        <is>
-          <t>Implementacion de componentes base (UrlInput, VerdictDisplay, ConfidenceBar, RedFlags, SimilarNews, LanguageToggle)</t>
-        </is>
-      </c>
-      <c r="E41" s="15" t="inlineStr">
-        <is>
-          <t>Luis</t>
-        </is>
-      </c>
-      <c r="F41" s="10" t="n">
-        <v>46137</v>
-      </c>
-      <c r="G41" s="10" t="n">
-        <v>46151</v>
-      </c>
-      <c r="H41" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="I41" s="8" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="J41" s="11" t="inlineStr">
-        <is>
-          <t>Completado</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="24" customHeight="1">
-      <c r="A42" s="6" t="n"/>
-      <c r="B42" s="7" t="inlineStr">
-        <is>
-          <t>Sprint</t>
-        </is>
-      </c>
-      <c r="C42" s="8" t="n">
-        <v>28</v>
-      </c>
-      <c r="D42" s="6" t="inlineStr">
-        <is>
-          <t>Implementacion de manejo de estados (loading, error, results) en App.tsx</t>
-        </is>
-      </c>
-      <c r="E42" s="15" t="inlineStr">
-        <is>
-          <t>Luis</t>
-        </is>
-      </c>
-      <c r="F42" s="10" t="n">
-        <v>46152</v>
-      </c>
-      <c r="G42" s="10" t="n">
-        <v>46160</v>
-      </c>
-      <c r="H42" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I42" s="8" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="J42" s="11" t="inlineStr">
-        <is>
-          <t>Completado</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="24" customHeight="1">
-      <c r="A43" s="16" t="n"/>
-      <c r="B43" s="17" t="inlineStr">
-        <is>
-          <t>Iteracion</t>
-        </is>
-      </c>
-      <c r="C43" s="17" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="D43" s="16" t="inlineStr">
-        <is>
-          <t>v0.5.0 - UI completa con todos los componentes, estados y noticias similares</t>
-        </is>
-      </c>
-      <c r="E43" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F43" s="18" t="n">
-        <v>46161</v>
-      </c>
-      <c r="G43" s="18" t="n">
-        <v>46162</v>
-      </c>
-      <c r="H43" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="I43" s="17" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="J43" s="17" t="inlineStr">
-        <is>
-          <t>Lanzado</t>
+      <c r="I43" s="8" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="J43" s="11" t="inlineStr">
+        <is>
+          <t>Completado</t>
         </is>
       </c>
     </row>
@@ -2249,30 +2206,30 @@
         </is>
       </c>
       <c r="C44" s="8" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>Implementacion de soporte bilingue ES/EN en todos los componentes</t>
-        </is>
-      </c>
-      <c r="E44" s="15" t="inlineStr">
+          <t>Componentes base: VerdictDisplay, ConfidenceBar, veredicto por color</t>
+        </is>
+      </c>
+      <c r="E44" s="13" t="inlineStr">
         <is>
           <t>Luis</t>
         </is>
       </c>
       <c r="F44" s="10" t="n">
-        <v>46161</v>
+        <v>46040</v>
       </c>
       <c r="G44" s="10" t="n">
-        <v>46169</v>
+        <v>46047</v>
       </c>
       <c r="H44" s="8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I44" s="8" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>87</t>
         </is>
       </c>
       <c r="J44" s="11" t="inlineStr">
@@ -2282,44 +2239,42 @@
       </c>
     </row>
     <row r="45" ht="24" customHeight="1">
-      <c r="A45" s="16" t="n"/>
-      <c r="B45" s="17" t="inlineStr">
-        <is>
-          <t>Iteracion</t>
-        </is>
-      </c>
-      <c r="C45" s="17" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="D45" s="16" t="inlineStr">
-        <is>
-          <t>v0.6.0 - Soporte bilingue ES/EN implementado</t>
-        </is>
-      </c>
-      <c r="E45" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F45" s="18" t="n">
-        <v>46170</v>
-      </c>
-      <c r="G45" s="18" t="n">
-        <v>46171</v>
-      </c>
-      <c r="H45" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="I45" s="17" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="J45" s="17" t="inlineStr">
-        <is>
-          <t>Lanzado</t>
+      <c r="A45" s="6" t="n"/>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="C45" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>Resultados esperados, metricas de evaluacion y criterios de exito</t>
+        </is>
+      </c>
+      <c r="E45" s="14" t="inlineStr">
+        <is>
+          <t>Ulises</t>
+        </is>
+      </c>
+      <c r="F45" s="10" t="n">
+        <v>46040</v>
+      </c>
+      <c r="G45" s="10" t="n">
+        <v>46049</v>
+      </c>
+      <c r="H45" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="I45" s="8" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="J45" s="11" t="inlineStr">
+        <is>
+          <t>Completado</t>
         </is>
       </c>
     </row>
@@ -2331,30 +2286,30 @@
         </is>
       </c>
       <c r="C46" s="8" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>Implementacion de article_type (5 tipos) y deteccion de estafas (is_scam)</t>
-        </is>
-      </c>
-      <c r="E46" s="13" t="inlineStr">
+          <t>Configuracion de pruebas: pytest, vitest, jsdom, testing-library</t>
+        </is>
+      </c>
+      <c r="E46" s="12" t="inlineStr">
         <is>
           <t>Marco</t>
         </is>
       </c>
       <c r="F46" s="10" t="n">
-        <v>46170</v>
+        <v>46040</v>
       </c>
       <c r="G46" s="10" t="n">
-        <v>46178</v>
+        <v>46048</v>
       </c>
       <c r="H46" s="8" t="n">
         <v>9</v>
       </c>
       <c r="I46" s="8" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>87</t>
         </is>
       </c>
       <c r="J46" s="11" t="inlineStr">
@@ -2364,44 +2319,42 @@
       </c>
     </row>
     <row r="47" ht="24" customHeight="1">
-      <c r="A47" s="16" t="n"/>
-      <c r="B47" s="17" t="inlineStr">
-        <is>
-          <t>Iteracion</t>
-        </is>
-      </c>
-      <c r="C47" s="17" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="D47" s="16" t="inlineStr">
-        <is>
-          <t>v0.7.0 - Clasificacion avanzada: tipo de articulo y deteccion de estafas</t>
-        </is>
-      </c>
-      <c r="E47" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F47" s="18" t="n">
-        <v>46179</v>
-      </c>
-      <c r="G47" s="18" t="n">
-        <v>46180</v>
-      </c>
-      <c r="H47" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="I47" s="17" t="inlineStr">
+      <c r="A47" s="6" t="n"/>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="C47" s="8" t="n">
+        <v>34</v>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>Scraper multi-estrategia: cloudscraper, curl_cffi, requests, Playwright</t>
+        </is>
+      </c>
+      <c r="E47" s="12" t="inlineStr">
+        <is>
+          <t>Marco</t>
+        </is>
+      </c>
+      <c r="F47" s="10" t="n">
+        <v>46049</v>
+      </c>
+      <c r="G47" s="10" t="n">
+        <v>46061</v>
+      </c>
+      <c r="H47" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="I47" s="8" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="J47" s="17" t="inlineStr">
-        <is>
-          <t>Lanzado</t>
+      <c r="J47" s="11" t="inlineStr">
+        <is>
+          <t>Completado</t>
         </is>
       </c>
     </row>
@@ -2413,30 +2366,30 @@
         </is>
       </c>
       <c r="C48" s="8" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>Diseno visual cyberpunk: animacion de cuadricula, glitch, vignette CRT, scanlines, clip-paths</t>
-        </is>
-      </c>
-      <c r="E48" s="15" t="inlineStr">
+          <t>Componentes: RedFlags, SimilarNews, LanguageToggle con estilos</t>
+        </is>
+      </c>
+      <c r="E48" s="13" t="inlineStr">
         <is>
           <t>Luis</t>
         </is>
       </c>
       <c r="F48" s="10" t="n">
-        <v>46179</v>
+        <v>46048</v>
       </c>
       <c r="G48" s="10" t="n">
-        <v>46191</v>
+        <v>46059</v>
       </c>
       <c r="H48" s="8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I48" s="8" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
       <c r="J48" s="11" t="inlineStr">
@@ -2446,44 +2399,42 @@
       </c>
     </row>
     <row r="49" ht="24" customHeight="1">
-      <c r="A49" s="16" t="n"/>
-      <c r="B49" s="17" t="inlineStr">
-        <is>
-          <t>Iteracion</t>
-        </is>
-      </c>
-      <c r="C49" s="17" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="D49" s="16" t="inlineStr">
-        <is>
-          <t>v0.8.0 - Diseno visual cyberpunk finalizado</t>
-        </is>
-      </c>
-      <c r="E49" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F49" s="18" t="n">
-        <v>46192</v>
-      </c>
-      <c r="G49" s="18" t="n">
-        <v>46193</v>
-      </c>
-      <c r="H49" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="I49" s="17" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="J49" s="17" t="inlineStr">
-        <is>
-          <t>Lanzado</t>
+      <c r="A49" s="6" t="n"/>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="C49" s="8" t="n">
+        <v>36</v>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>Documentacion de avances del Capitulo 4: Desarrollo e Implementacion</t>
+        </is>
+      </c>
+      <c r="E49" s="14" t="inlineStr">
+        <is>
+          <t>Ulises</t>
+        </is>
+      </c>
+      <c r="F49" s="10" t="n">
+        <v>46050</v>
+      </c>
+      <c r="G49" s="10" t="n">
+        <v>46063</v>
+      </c>
+      <c r="H49" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="I49" s="8" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="J49" s="11" t="inlineStr">
+        <is>
+          <t>Completado</t>
         </is>
       </c>
     </row>
@@ -2495,30 +2446,30 @@
         </is>
       </c>
       <c r="C50" s="8" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>Redaccion del Capitulo 4: Desarrollo e Implementacion (concurrente con programacion)</t>
+          <t>Pruebas del scraper y validacion de extraccion de contenido HTML</t>
         </is>
       </c>
       <c r="E50" s="12" t="inlineStr">
         <is>
-          <t>Ulises</t>
+          <t>Marco</t>
         </is>
       </c>
       <c r="F50" s="10" t="n">
-        <v>46192</v>
+        <v>46049</v>
       </c>
       <c r="G50" s="10" t="n">
-        <v>46212</v>
+        <v>46061</v>
       </c>
       <c r="H50" s="8" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="I50" s="8" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>33</t>
         </is>
       </c>
       <c r="J50" s="11" t="inlineStr">
@@ -2528,36 +2479,86 @@
       </c>
     </row>
     <row r="51" ht="24" customHeight="1">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>Ciclo 4: Validacion y Despliegue</t>
-        </is>
-      </c>
-      <c r="B51" s="3" t="n"/>
-      <c r="C51" s="3" t="n"/>
-      <c r="D51" s="3" t="n"/>
-      <c r="E51" s="3" t="n"/>
-      <c r="F51" s="3" t="n"/>
-      <c r="G51" s="3" t="n"/>
-      <c r="H51" s="3" t="n"/>
-      <c r="I51" s="3" t="n"/>
-      <c r="J51" s="3" t="n"/>
+      <c r="A51" s="15" t="n"/>
+      <c r="B51" s="16" t="inlineStr">
+        <is>
+          <t>Iteracion</t>
+        </is>
+      </c>
+      <c r="C51" s="16" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="D51" s="15" t="inlineStr">
+        <is>
+          <t>v0.3.0 - Scraper multi-estrategia funcional: cloudscraper, curl_cffi, requests y Playwright integrados y validados</t>
+        </is>
+      </c>
+      <c r="E51" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F51" s="17" t="n">
+        <v>46062</v>
+      </c>
+      <c r="G51" s="17" t="n">
+        <v>46063</v>
+      </c>
+      <c r="H51" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="I51" s="16" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="J51" s="16" t="inlineStr">
+        <is>
+          <t>Lanzado</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="24" customHeight="1">
-      <c r="A52" s="4" t="inlineStr">
-        <is>
-          <t>Fase 4: Pruebas y Despliegue</t>
-        </is>
-      </c>
-      <c r="B52" s="5" t="n"/>
-      <c r="C52" s="5" t="n"/>
-      <c r="D52" s="5" t="n"/>
-      <c r="E52" s="5" t="n"/>
-      <c r="F52" s="5" t="n"/>
-      <c r="G52" s="5" t="n"/>
-      <c r="H52" s="5" t="n"/>
-      <c r="I52" s="5" t="n"/>
-      <c r="J52" s="5" t="n"/>
+      <c r="A52" s="6" t="n"/>
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="C52" s="8" t="n">
+        <v>38</v>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>Llamadas a Groq API: call_groq, prompt engineering, parse_response</t>
+        </is>
+      </c>
+      <c r="E52" s="12" t="inlineStr">
+        <is>
+          <t>Marco</t>
+        </is>
+      </c>
+      <c r="F52" s="10" t="n">
+        <v>46062</v>
+      </c>
+      <c r="G52" s="10" t="n">
+        <v>46074</v>
+      </c>
+      <c r="H52" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="I52" s="8" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="J52" s="11" t="inlineStr">
+        <is>
+          <t>Completado</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="24" customHeight="1">
       <c r="A53" s="6" t="n"/>
@@ -2567,30 +2568,30 @@
         </is>
       </c>
       <c r="C53" s="8" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>Creacion de suite de pruebas backend (server/test_analyzer.py, pytest)</t>
+          <t>Manejo de estados (loading, error, results) y soporte bilingue ES/EN</t>
         </is>
       </c>
       <c r="E53" s="13" t="inlineStr">
         <is>
-          <t>Marco</t>
+          <t>Luis</t>
         </is>
       </c>
       <c r="F53" s="10" t="n">
-        <v>46213</v>
+        <v>46060</v>
       </c>
       <c r="G53" s="10" t="n">
-        <v>46223</v>
+        <v>46071</v>
       </c>
       <c r="H53" s="8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I53" s="8" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J53" s="11" t="inlineStr">
@@ -2607,30 +2608,30 @@
         </is>
       </c>
       <c r="C54" s="8" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>Creacion de suite de pruebas frontend (vitest + testing-library, 7 archivos, 52 tests)</t>
-        </is>
-      </c>
-      <c r="E54" s="13" t="inlineStr">
-        <is>
-          <t>Marco</t>
+          <t>Actualizacion Capitulos 1-3 segun cambios de implementacion</t>
+        </is>
+      </c>
+      <c r="E54" s="14" t="inlineStr">
+        <is>
+          <t>Ulises</t>
         </is>
       </c>
       <c r="F54" s="10" t="n">
-        <v>46224</v>
+        <v>46064</v>
       </c>
       <c r="G54" s="10" t="n">
-        <v>46234</v>
+        <v>46077</v>
       </c>
       <c r="H54" s="8" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I54" s="8" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>36</t>
         </is>
       </c>
       <c r="J54" s="11" t="inlineStr">
@@ -2647,30 +2648,30 @@
         </is>
       </c>
       <c r="C55" s="8" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>Configuracion de despliegue (Procfile con gunicorn, variables de entorno, CORS)</t>
+          <t>Pruebas de integracion scraper + Groq API con distintos tipos de URL</t>
         </is>
       </c>
       <c r="E55" s="13" t="inlineStr">
         <is>
-          <t>Marco</t>
+          <t>Luis</t>
         </is>
       </c>
       <c r="F55" s="10" t="n">
-        <v>46235</v>
+        <v>46062</v>
       </c>
       <c r="G55" s="10" t="n">
-        <v>46240</v>
+        <v>46074</v>
       </c>
       <c r="H55" s="8" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="I55" s="8" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>37</t>
         </is>
       </c>
       <c r="J55" s="11" t="inlineStr">
@@ -2687,30 +2688,30 @@
         </is>
       </c>
       <c r="C56" s="8" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>Despliegue en Railway (fallo por limitaciones, migracion a Render)</t>
-        </is>
-      </c>
-      <c r="E56" s="13" t="inlineStr">
+          <t>Clasificador de credibilidad: 5 categorias, CREDIBLE_DOMAINS y override</t>
+        </is>
+      </c>
+      <c r="E56" s="12" t="inlineStr">
         <is>
           <t>Marco</t>
         </is>
       </c>
       <c r="F56" s="10" t="n">
-        <v>46241</v>
+        <v>46075</v>
       </c>
       <c r="G56" s="10" t="n">
-        <v>46248</v>
+        <v>46087</v>
       </c>
       <c r="H56" s="8" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="I56" s="8" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>38</t>
         </is>
       </c>
       <c r="J56" s="11" t="inlineStr">
@@ -2727,30 +2728,30 @@
         </is>
       </c>
       <c r="C57" s="8" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>Despliegue exitoso en Render con dominio publico</t>
+          <t>Diseno visual cyberpunk: cuadricula, glitch, vignette CRT, scanlines</t>
         </is>
       </c>
       <c r="E57" s="13" t="inlineStr">
         <is>
-          <t>Marco</t>
+          <t>Luis</t>
         </is>
       </c>
       <c r="F57" s="10" t="n">
-        <v>46249</v>
+        <v>46072</v>
       </c>
       <c r="G57" s="10" t="n">
-        <v>46257</v>
+        <v>46083</v>
       </c>
       <c r="H57" s="8" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I57" s="8" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>39</t>
         </is>
       </c>
       <c r="J57" s="11" t="inlineStr">
@@ -2760,44 +2761,42 @@
       </c>
     </row>
     <row r="58" ht="24" customHeight="1">
-      <c r="A58" s="16" t="n"/>
-      <c r="B58" s="17" t="inlineStr">
-        <is>
-          <t>Iteracion</t>
-        </is>
-      </c>
-      <c r="C58" s="17" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="D58" s="16" t="inlineStr">
-        <is>
-          <t>v1.0.0 - Version estable desplegada en Render con dominio publico</t>
-        </is>
-      </c>
-      <c r="E58" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F58" s="18" t="n">
-        <v>46258</v>
-      </c>
-      <c r="G58" s="18" t="n">
-        <v>46259</v>
-      </c>
-      <c r="H58" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="I58" s="17" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="J58" s="17" t="inlineStr">
-        <is>
-          <t>Lanzado</t>
+      <c r="A58" s="6" t="n"/>
+      <c r="B58" s="7" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="C58" s="8" t="n">
+        <v>44</v>
+      </c>
+      <c r="D58" s="6" t="inlineStr">
+        <is>
+          <t>Tabla de resultados, analisis preliminar de datos e indice de tesis</t>
+        </is>
+      </c>
+      <c r="E58" s="14" t="inlineStr">
+        <is>
+          <t>Ulises</t>
+        </is>
+      </c>
+      <c r="F58" s="10" t="n">
+        <v>46078</v>
+      </c>
+      <c r="G58" s="10" t="n">
+        <v>46091</v>
+      </c>
+      <c r="H58" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="I58" s="8" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J58" s="11" t="inlineStr">
+        <is>
+          <t>Completado</t>
         </is>
       </c>
     </row>
@@ -2809,30 +2808,30 @@
         </is>
       </c>
       <c r="C59" s="8" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>Capturas de pantalla del sistema (interfaz, analisis, resultados, errores, mockups)</t>
-        </is>
-      </c>
-      <c r="E59" s="15" t="inlineStr">
+          <t>Pruebas de integracion frontend-backend con datos simulados y reales</t>
+        </is>
+      </c>
+      <c r="E59" s="13" t="inlineStr">
         <is>
           <t>Luis</t>
         </is>
       </c>
       <c r="F59" s="10" t="n">
-        <v>46258</v>
+        <v>46075</v>
       </c>
       <c r="G59" s="10" t="n">
-        <v>46263</v>
+        <v>46087</v>
       </c>
       <c r="H59" s="8" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="I59" s="8" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>41</t>
         </is>
       </c>
       <c r="J59" s="11" t="inlineStr">
@@ -2842,36 +2841,86 @@
       </c>
     </row>
     <row r="60" ht="24" customHeight="1">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>Ciclo 5: Resultados y Documentacion Final</t>
-        </is>
-      </c>
-      <c r="B60" s="3" t="n"/>
-      <c r="C60" s="3" t="n"/>
-      <c r="D60" s="3" t="n"/>
-      <c r="E60" s="3" t="n"/>
-      <c r="F60" s="3" t="n"/>
-      <c r="G60" s="3" t="n"/>
-      <c r="H60" s="3" t="n"/>
-      <c r="I60" s="3" t="n"/>
-      <c r="J60" s="3" t="n"/>
+      <c r="A60" s="15" t="n"/>
+      <c r="B60" s="16" t="inlineStr">
+        <is>
+          <t>Iteracion</t>
+        </is>
+      </c>
+      <c r="C60" s="16" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="D60" s="15" t="inlineStr">
+        <is>
+          <t>v0.4.0 - Clasificador de credibilidad, integracion frontend-backend y diseno cyberpunk completos</t>
+        </is>
+      </c>
+      <c r="E60" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F60" s="17" t="n">
+        <v>46088</v>
+      </c>
+      <c r="G60" s="17" t="n">
+        <v>46089</v>
+      </c>
+      <c r="H60" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="I60" s="16" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J60" s="16" t="inlineStr">
+        <is>
+          <t>Lanzado</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="24" customHeight="1">
-      <c r="A61" s="4" t="inlineStr">
-        <is>
-          <t>Fase 5: Resultados y Documentacion</t>
-        </is>
-      </c>
-      <c r="B61" s="5" t="n"/>
-      <c r="C61" s="5" t="n"/>
-      <c r="D61" s="5" t="n"/>
-      <c r="E61" s="5" t="n"/>
-      <c r="F61" s="5" t="n"/>
-      <c r="G61" s="5" t="n"/>
-      <c r="H61" s="5" t="n"/>
-      <c r="I61" s="5" t="n"/>
-      <c r="J61" s="5" t="n"/>
+      <c r="A61" s="6" t="n"/>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="C61" s="8" t="n">
+        <v>46</v>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>Busqueda de noticias similares: news_finder.py, Google News RSS</t>
+        </is>
+      </c>
+      <c r="E61" s="12" t="inlineStr">
+        <is>
+          <t>Marco</t>
+        </is>
+      </c>
+      <c r="F61" s="10" t="n">
+        <v>46088</v>
+      </c>
+      <c r="G61" s="10" t="n">
+        <v>46100</v>
+      </c>
+      <c r="H61" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="I61" s="8" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="J61" s="11" t="inlineStr">
+        <is>
+          <t>Completado</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="24" customHeight="1">
       <c r="A62" s="6" t="n"/>
@@ -2881,35 +2930,35 @@
         </is>
       </c>
       <c r="C62" s="8" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t>Pruebas de analisis con URLs reales (positivas, negativas, estafas, satira, opinion)</t>
+          <t>Conexion frontend-backend via API REST (fetch /analyze + AbortController)</t>
         </is>
       </c>
       <c r="E62" s="13" t="inlineStr">
         <is>
-          <t>Marco</t>
+          <t>Luis</t>
         </is>
       </c>
       <c r="F62" s="10" t="n">
-        <v>46258</v>
+        <v>46084</v>
       </c>
       <c r="G62" s="10" t="n">
-        <v>46272</v>
+        <v>46095</v>
       </c>
       <c r="H62" s="8" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I62" s="8" t="inlineStr">
         <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="J62" s="19" t="inlineStr">
-        <is>
-          <t>En Progreso</t>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="J62" s="11" t="inlineStr">
+        <is>
+          <t>Completado</t>
         </is>
       </c>
     </row>
@@ -2921,77 +2970,75 @@
         </is>
       </c>
       <c r="C63" s="8" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>Correccion de errores: timeouts (AbortController 60s), override dominios, edge cases</t>
-        </is>
-      </c>
-      <c r="E63" s="13" t="inlineStr">
-        <is>
-          <t>Marco</t>
+          <t>Referencias bibliograficas, anexos y plantilla oficial de tesis</t>
+        </is>
+      </c>
+      <c r="E63" s="14" t="inlineStr">
+        <is>
+          <t>Ulises</t>
         </is>
       </c>
       <c r="F63" s="10" t="n">
-        <v>46273</v>
+        <v>46092</v>
       </c>
       <c r="G63" s="10" t="n">
-        <v>46285</v>
+        <v>46105</v>
       </c>
       <c r="H63" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="I63" s="8" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="J63" s="11" t="inlineStr">
+        <is>
+          <t>Completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="24" customHeight="1">
+      <c r="A64" s="6" t="n"/>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="C64" s="8" t="n">
+        <v>49</v>
+      </c>
+      <c r="D64" s="6" t="inlineStr">
+        <is>
+          <t>Pruebas de regresion y deteccion de defectos en integracion continua</t>
+        </is>
+      </c>
+      <c r="E64" s="13" t="inlineStr">
+        <is>
+          <t>Luis</t>
+        </is>
+      </c>
+      <c r="F64" s="10" t="n">
+        <v>46088</v>
+      </c>
+      <c r="G64" s="10" t="n">
+        <v>46100</v>
+      </c>
+      <c r="H64" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="I63" s="8" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="J63" s="19" t="inlineStr">
-        <is>
-          <t>En Progreso</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="24" customHeight="1">
-      <c r="A64" s="16" t="n"/>
-      <c r="B64" s="17" t="inlineStr">
-        <is>
-          <t>Iteracion</t>
-        </is>
-      </c>
-      <c r="C64" s="17" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="D64" s="16" t="inlineStr">
-        <is>
-          <t>v1.1.0 - Refinamiento y correccion de errores del clasificador</t>
-        </is>
-      </c>
-      <c r="E64" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F64" s="18" t="n">
-        <v>46286</v>
-      </c>
-      <c r="G64" s="18" t="n">
-        <v>46287</v>
-      </c>
-      <c r="H64" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="I64" s="17" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J64" s="17" t="inlineStr">
-        <is>
-          <t>Lanzado</t>
+      <c r="I64" s="8" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J64" s="11" t="inlineStr">
+        <is>
+          <t>Completado</t>
         </is>
       </c>
     </row>
@@ -3003,35 +3050,35 @@
         </is>
       </c>
       <c r="C65" s="8" t="n">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>Analisis de casos de prueba y documentacion de resultados</t>
-        </is>
-      </c>
-      <c r="E65" s="14" t="inlineStr">
-        <is>
-          <t>Tony</t>
+          <t>Article_type: 5 tipos y ajustes finales de clasificacion</t>
+        </is>
+      </c>
+      <c r="E65" s="12" t="inlineStr">
+        <is>
+          <t>Marco</t>
         </is>
       </c>
       <c r="F65" s="10" t="n">
-        <v>46286</v>
+        <v>46101</v>
       </c>
       <c r="G65" s="10" t="n">
-        <v>46296</v>
+        <v>46111</v>
       </c>
       <c r="H65" s="8" t="n">
         <v>11</v>
       </c>
       <c r="I65" s="8" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J65" s="20" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="J65" s="11" t="inlineStr">
+        <is>
+          <t>Completado</t>
         </is>
       </c>
     </row>
@@ -3043,35 +3090,35 @@
         </is>
       </c>
       <c r="C66" s="8" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
-          <t>Redaccion del Capitulo 5: Resultados, pruebas y conclusiones</t>
-        </is>
-      </c>
-      <c r="E66" s="12" t="inlineStr">
-        <is>
-          <t>Ulises</t>
+          <t>Manejo de errores de red, timeouts y UX de carga animada</t>
+        </is>
+      </c>
+      <c r="E66" s="13" t="inlineStr">
+        <is>
+          <t>Luis</t>
         </is>
       </c>
       <c r="F66" s="10" t="n">
-        <v>46297</v>
+        <v>46096</v>
       </c>
       <c r="G66" s="10" t="n">
-        <v>46311</v>
+        <v>46105</v>
       </c>
       <c r="H66" s="8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I66" s="8" t="inlineStr">
         <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="J66" s="20" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="J66" s="11" t="inlineStr">
+        <is>
+          <t>Completado</t>
         </is>
       </c>
     </row>
@@ -3083,35 +3130,35 @@
         </is>
       </c>
       <c r="C67" s="8" t="n">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>Redaccion de introduccion, resumen y abstract de la tesis</t>
-        </is>
-      </c>
-      <c r="E67" s="12" t="inlineStr">
+          <t>Resultados parciales, graficas y tablas de visualizacion</t>
+        </is>
+      </c>
+      <c r="E67" s="14" t="inlineStr">
         <is>
           <t>Ulises</t>
         </is>
       </c>
       <c r="F67" s="10" t="n">
-        <v>46312</v>
+        <v>46106</v>
       </c>
       <c r="G67" s="10" t="n">
-        <v>46317</v>
+        <v>46117</v>
       </c>
       <c r="H67" s="8" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I67" s="8" t="inlineStr">
         <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="J67" s="20" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="J67" s="11" t="inlineStr">
+        <is>
+          <t>Completado</t>
         </is>
       </c>
     </row>
@@ -3123,75 +3170,77 @@
         </is>
       </c>
       <c r="C68" s="8" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t>Creacion del diagrama de Gantt del proyecto (Gantt_VERIFEX.xlsx)</t>
-        </is>
-      </c>
-      <c r="E68" s="12" t="inlineStr">
+          <t>Pruebas de aceptacion de usuario (UAT) con escenarios reales</t>
+        </is>
+      </c>
+      <c r="E68" s="14" t="inlineStr">
         <is>
           <t>Ulises</t>
         </is>
       </c>
       <c r="F68" s="10" t="n">
-        <v>46318</v>
+        <v>46101</v>
       </c>
       <c r="G68" s="10" t="n">
-        <v>46322</v>
+        <v>46111</v>
       </c>
       <c r="H68" s="8" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="I68" s="8" t="inlineStr">
         <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="J68" s="20" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="J68" s="11" t="inlineStr">
+        <is>
+          <t>Completado</t>
         </is>
       </c>
     </row>
     <row r="69" ht="24" customHeight="1">
-      <c r="A69" s="6" t="n"/>
-      <c r="B69" s="7" t="inlineStr">
-        <is>
-          <t>Sprint</t>
-        </is>
-      </c>
-      <c r="C69" s="8" t="n">
-        <v>45</v>
-      </c>
-      <c r="D69" s="6" t="inlineStr">
-        <is>
-          <t>Creacion del tablero Kanban del proyecto (Kanban_VERIFEX.xlsx)</t>
-        </is>
-      </c>
-      <c r="E69" s="12" t="inlineStr">
-        <is>
-          <t>Ulises</t>
-        </is>
-      </c>
-      <c r="F69" s="10" t="n">
-        <v>46323</v>
-      </c>
-      <c r="G69" s="10" t="n">
-        <v>46326</v>
-      </c>
-      <c r="H69" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="I69" s="8" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="J69" s="20" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
+      <c r="A69" s="15" t="n"/>
+      <c r="B69" s="16" t="inlineStr">
+        <is>
+          <t>Iteracion</t>
+        </is>
+      </c>
+      <c r="C69" s="16" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="D69" s="15" t="inlineStr">
+        <is>
+          <t>v0.5.0 - Desarrollo completo: scraper, IA, clasificador, news_finder, UI cyberpunk y pruebas de integracion</t>
+        </is>
+      </c>
+      <c r="E69" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F69" s="17" t="n">
+        <v>46112</v>
+      </c>
+      <c r="G69" s="17" t="n">
+        <v>46113</v>
+      </c>
+      <c r="H69" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="I69" s="16" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="J69" s="16" t="inlineStr">
+        <is>
+          <t>Lanzado</t>
         </is>
       </c>
     </row>
@@ -3203,117 +3252,69 @@
         </is>
       </c>
       <c r="C70" s="8" t="n">
-        <v>46</v>
+        <v>88</v>
       </c>
       <c r="D70" s="6" t="inlineStr">
         <is>
-          <t>Maquetacion y formato del documento Word (estilos, indices, referencias, portada)</t>
-        </is>
-      </c>
-      <c r="E70" s="12" t="inlineStr">
-        <is>
-          <t>Ulises</t>
+          <t>Revision Ciclo 3: validacion del desarrollo completo y correcciones</t>
+        </is>
+      </c>
+      <c r="E70" s="9" t="inlineStr">
+        <is>
+          <t>Todos</t>
         </is>
       </c>
       <c r="F70" s="10" t="n">
-        <v>46327</v>
+        <v>46112</v>
       </c>
       <c r="G70" s="10" t="n">
-        <v>46334</v>
+        <v>46117</v>
       </c>
       <c r="H70" s="8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I70" s="8" t="inlineStr">
         <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J70" s="20" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="J70" s="11" t="inlineStr">
+        <is>
+          <t>Completado</t>
         </is>
       </c>
     </row>
     <row r="71" ht="24" customHeight="1">
-      <c r="A71" s="6" t="n"/>
-      <c r="B71" s="7" t="inlineStr">
-        <is>
-          <t>Sprint</t>
-        </is>
-      </c>
-      <c r="C71" s="8" t="n">
-        <v>47</v>
-      </c>
-      <c r="D71" s="6" t="inlineStr">
-        <is>
-          <t>Revision de contenido, ortografia y consistencia de la tesis</t>
-        </is>
-      </c>
-      <c r="E71" s="14" t="inlineStr">
-        <is>
-          <t>Tony</t>
-        </is>
-      </c>
-      <c r="F71" s="10" t="n">
-        <v>46335</v>
-      </c>
-      <c r="G71" s="10" t="n">
-        <v>46341</v>
-      </c>
-      <c r="H71" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="I71" s="8" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="J71" s="20" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>Ciclo 4: Validacion y Despliegue</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="n"/>
+      <c r="C71" s="3" t="n"/>
+      <c r="D71" s="3" t="n"/>
+      <c r="E71" s="3" t="n"/>
+      <c r="F71" s="3" t="n"/>
+      <c r="G71" s="3" t="n"/>
+      <c r="H71" s="3" t="n"/>
+      <c r="I71" s="3" t="n"/>
+      <c r="J71" s="3" t="n"/>
     </row>
     <row r="72" ht="24" customHeight="1">
-      <c r="A72" s="6" t="n"/>
-      <c r="B72" s="7" t="inlineStr">
-        <is>
-          <t>Sprint</t>
-        </is>
-      </c>
-      <c r="C72" s="8" t="n">
-        <v>48</v>
-      </c>
-      <c r="D72" s="6" t="inlineStr">
-        <is>
-          <t>Correcciones finales y ajustes segun retroalimentacion</t>
-        </is>
-      </c>
-      <c r="E72" s="12" t="inlineStr">
-        <is>
-          <t>Ulises</t>
-        </is>
-      </c>
-      <c r="F72" s="10" t="n">
-        <v>46342</v>
-      </c>
-      <c r="G72" s="10" t="n">
-        <v>46347</v>
-      </c>
-      <c r="H72" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="I72" s="8" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="J72" s="20" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>Fase 4: Validacion y Despliegue</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="n"/>
+      <c r="C72" s="5" t="n"/>
+      <c r="D72" s="5" t="n"/>
+      <c r="E72" s="5" t="n"/>
+      <c r="F72" s="5" t="n"/>
+      <c r="G72" s="5" t="n"/>
+      <c r="H72" s="5" t="n"/>
+      <c r="I72" s="5" t="n"/>
+      <c r="J72" s="5" t="n"/>
     </row>
     <row r="73" ht="24" customHeight="1">
       <c r="A73" s="6" t="n"/>
@@ -3323,181 +3324,1816 @@
         </is>
       </c>
       <c r="C73" s="8" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>Generacion de PDF final de tesis (TESIS_VERIFEX.pdf)</t>
+          <t>Suite pruebas backend: 27 tests en server/test_analyzer.py (pytest)</t>
         </is>
       </c>
       <c r="E73" s="12" t="inlineStr">
         <is>
+          <t>Marco</t>
+        </is>
+      </c>
+      <c r="F73" s="10" t="n">
+        <v>46118</v>
+      </c>
+      <c r="G73" s="10" t="n">
+        <v>46130</v>
+      </c>
+      <c r="H73" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="I73" s="8" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="J73" s="11" t="inlineStr">
+        <is>
+          <t>Completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="24" customHeight="1">
+      <c r="A74" s="6" t="n"/>
+      <c r="B74" s="7" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="C74" s="8" t="n">
+        <v>55</v>
+      </c>
+      <c r="D74" s="6" t="inlineStr">
+        <is>
+          <t>Suite pruebas frontend: 52 tests con vitest + testing-library</t>
+        </is>
+      </c>
+      <c r="E74" s="13" t="inlineStr">
+        <is>
+          <t>Luis</t>
+        </is>
+      </c>
+      <c r="F74" s="10" t="n">
+        <v>46118</v>
+      </c>
+      <c r="G74" s="10" t="n">
+        <v>46129</v>
+      </c>
+      <c r="H74" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I74" s="8" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="J74" s="11" t="inlineStr">
+        <is>
+          <t>Completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="24" customHeight="1">
+      <c r="A75" s="6" t="n"/>
+      <c r="B75" s="7" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="C75" s="8" t="n">
+        <v>56</v>
+      </c>
+      <c r="D75" s="6" t="inlineStr">
+        <is>
+          <t>Resultados detallados y analisis de datos recopilados</t>
+        </is>
+      </c>
+      <c r="E75" s="14" t="inlineStr">
+        <is>
           <t>Ulises</t>
         </is>
       </c>
-      <c r="F73" s="10" t="n">
-        <v>46348</v>
-      </c>
-      <c r="G73" s="10" t="n">
-        <v>46351</v>
-      </c>
-      <c r="H73" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="I73" s="8" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="J73" s="20" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="24" customHeight="1">
-      <c r="A74" s="16" t="n"/>
-      <c r="B74" s="17" t="inlineStr">
+      <c r="F75" s="10" t="n">
+        <v>46118</v>
+      </c>
+      <c r="G75" s="10" t="n">
+        <v>46131</v>
+      </c>
+      <c r="H75" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="I75" s="8" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="J75" s="11" t="inlineStr">
+        <is>
+          <t>Completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="24" customHeight="1">
+      <c r="A76" s="6" t="n"/>
+      <c r="B76" s="7" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="C76" s="8" t="n">
+        <v>57</v>
+      </c>
+      <c r="D76" s="6" t="inlineStr">
+        <is>
+          <t>Documentacion de pruebas: defectos, cobertura y metricas</t>
+        </is>
+      </c>
+      <c r="E76" s="14" t="inlineStr">
+        <is>
+          <t>Ulises</t>
+        </is>
+      </c>
+      <c r="F76" s="10" t="n">
+        <v>46118</v>
+      </c>
+      <c r="G76" s="10" t="n">
+        <v>46130</v>
+      </c>
+      <c r="H76" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="I76" s="8" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="J76" s="11" t="inlineStr">
+        <is>
+          <t>Completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="24" customHeight="1">
+      <c r="A77" s="15" t="n"/>
+      <c r="B77" s="16" t="inlineStr">
         <is>
           <t>Iteracion</t>
         </is>
       </c>
-      <c r="C74" s="17" t="inlineStr">
+      <c r="C77" s="16" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="D74" s="16" t="inlineStr">
-        <is>
-          <t>v1.2.0 - Version final de tesis con todas las funcionalidades implementadas y documentadas</t>
-        </is>
-      </c>
-      <c r="E74" s="17" t="inlineStr">
+      <c r="D77" s="15" t="inlineStr">
+        <is>
+          <t>v0.6.0 - Suites completas de pruebas backend y frontend, resultados documentados y metricas de cobertura</t>
+        </is>
+      </c>
+      <c r="E77" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F74" s="18" t="n">
-        <v>46352</v>
-      </c>
-      <c r="G74" s="18" t="n">
-        <v>46353</v>
-      </c>
-      <c r="H74" s="17" t="n">
+      <c r="F77" s="17" t="n">
+        <v>46131</v>
+      </c>
+      <c r="G77" s="17" t="n">
+        <v>46132</v>
+      </c>
+      <c r="H77" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="I74" s="17" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="J74" s="17" t="inlineStr">
+      <c r="I77" s="16" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="J77" s="16" t="inlineStr">
         <is>
           <t>Lanzado</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="24" customHeight="1"/>
-    <row r="76" ht="24" customHeight="1"/>
-    <row r="77" ht="24" customHeight="1">
-      <c r="A77" s="21" t="inlineStr">
+    <row r="78" ht="24" customHeight="1">
+      <c r="A78" s="6" t="n"/>
+      <c r="B78" s="7" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="C78" s="8" t="n">
+        <v>58</v>
+      </c>
+      <c r="D78" s="6" t="inlineStr">
+        <is>
+          <t>Configuracion despliegue: Procfile, build.sh, CORS, gunicorn, Railway</t>
+        </is>
+      </c>
+      <c r="E78" s="12" t="inlineStr">
+        <is>
+          <t>Marco</t>
+        </is>
+      </c>
+      <c r="F78" s="10" t="n">
+        <v>46131</v>
+      </c>
+      <c r="G78" s="10" t="n">
+        <v>46143</v>
+      </c>
+      <c r="H78" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="I78" s="8" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="J78" s="11" t="inlineStr">
+        <is>
+          <t>Completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="24" customHeight="1">
+      <c r="A79" s="6" t="n"/>
+      <c r="B79" s="7" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="C79" s="8" t="n">
+        <v>59</v>
+      </c>
+      <c r="D79" s="6" t="inlineStr">
+        <is>
+          <t>Capturas del sistema: interfaz, resultados, errores, responsive</t>
+        </is>
+      </c>
+      <c r="E79" s="13" t="inlineStr">
+        <is>
+          <t>Luis</t>
+        </is>
+      </c>
+      <c r="F79" s="10" t="n">
+        <v>46130</v>
+      </c>
+      <c r="G79" s="10" t="n">
+        <v>46141</v>
+      </c>
+      <c r="H79" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I79" s="8" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="J79" s="11" t="inlineStr">
+        <is>
+          <t>Completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="24" customHeight="1">
+      <c r="A80" s="6" t="n"/>
+      <c r="B80" s="7" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="C80" s="8" t="n">
+        <v>60</v>
+      </c>
+      <c r="D80" s="6" t="inlineStr">
+        <is>
+          <t>Actualizacion bibliografia, graficas y tablas de visualizacion</t>
+        </is>
+      </c>
+      <c r="E80" s="14" t="inlineStr">
+        <is>
+          <t>Ulises</t>
+        </is>
+      </c>
+      <c r="F80" s="10" t="n">
+        <v>46132</v>
+      </c>
+      <c r="G80" s="10" t="n">
+        <v>46145</v>
+      </c>
+      <c r="H80" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="I80" s="8" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="J80" s="11" t="inlineStr">
+        <is>
+          <t>Completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="24" customHeight="1">
+      <c r="A81" s="6" t="n"/>
+      <c r="B81" s="7" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="C81" s="8" t="n">
+        <v>61</v>
+      </c>
+      <c r="D81" s="6" t="inlineStr">
+        <is>
+          <t>Validacion de seguridad: manejo errores, proteccion API key, estres</t>
+        </is>
+      </c>
+      <c r="E81" s="12" t="inlineStr">
+        <is>
+          <t>Marco</t>
+        </is>
+      </c>
+      <c r="F81" s="10" t="n">
+        <v>46131</v>
+      </c>
+      <c r="G81" s="10" t="n">
+        <v>46143</v>
+      </c>
+      <c r="H81" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="I81" s="8" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="J81" s="11" t="inlineStr">
+        <is>
+          <t>Completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="24" customHeight="1">
+      <c r="A82" s="15" t="n"/>
+      <c r="B82" s="16" t="inlineStr">
+        <is>
+          <t>Iteracion</t>
+        </is>
+      </c>
+      <c r="C82" s="16" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="D82" s="15" t="inlineStr">
+        <is>
+          <t>v0.7.0 - Configuracion de despliegue, capturas del sistema, validacion de seguridad y bibliografia actualizada</t>
+        </is>
+      </c>
+      <c r="E82" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F82" s="17" t="n">
+        <v>46144</v>
+      </c>
+      <c r="G82" s="17" t="n">
+        <v>46145</v>
+      </c>
+      <c r="H82" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="I82" s="16" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="J82" s="16" t="inlineStr">
+        <is>
+          <t>Lanzado</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="24" customHeight="1">
+      <c r="A83" s="6" t="n"/>
+      <c r="B83" s="7" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="C83" s="8" t="n">
+        <v>62</v>
+      </c>
+      <c r="D83" s="6" t="inlineStr">
+        <is>
+          <t>Despliegue Railway → Render, dominio publico y SSL</t>
+        </is>
+      </c>
+      <c r="E83" s="12" t="inlineStr">
+        <is>
+          <t>Marco</t>
+        </is>
+      </c>
+      <c r="F83" s="10" t="n">
+        <v>46144</v>
+      </c>
+      <c r="G83" s="10" t="n">
+        <v>46156</v>
+      </c>
+      <c r="H83" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="I83" s="8" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="J83" s="11" t="inlineStr">
+        <is>
+          <t>Completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="24" customHeight="1">
+      <c r="A84" s="6" t="n"/>
+      <c r="B84" s="7" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="C84" s="8" t="n">
+        <v>63</v>
+      </c>
+      <c r="D84" s="6" t="inlineStr">
+        <is>
+          <t>Optimizacion frontend: lazy loading SimilarNews, code splitting</t>
+        </is>
+      </c>
+      <c r="E84" s="13" t="inlineStr">
+        <is>
+          <t>Luis</t>
+        </is>
+      </c>
+      <c r="F84" s="10" t="n">
+        <v>46142</v>
+      </c>
+      <c r="G84" s="10" t="n">
+        <v>46153</v>
+      </c>
+      <c r="H84" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I84" s="8" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="J84" s="11" t="inlineStr">
+        <is>
+          <t>Completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="24" customHeight="1">
+      <c r="A85" s="6" t="n"/>
+      <c r="B85" s="7" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="C85" s="8" t="n">
+        <v>64</v>
+      </c>
+      <c r="D85" s="6" t="inlineStr">
+        <is>
+          <t>Conclusiones preliminares y recomendaciones del proyecto</t>
+        </is>
+      </c>
+      <c r="E85" s="14" t="inlineStr">
+        <is>
+          <t>Ulises</t>
+        </is>
+      </c>
+      <c r="F85" s="10" t="n">
+        <v>46146</v>
+      </c>
+      <c r="G85" s="10" t="n">
+        <v>46159</v>
+      </c>
+      <c r="H85" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="I85" s="8" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J85" s="11" t="inlineStr">
+        <is>
+          <t>Completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="24" customHeight="1">
+      <c r="A86" s="6" t="n"/>
+      <c r="B86" s="7" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="C86" s="8" t="n">
+        <v>65</v>
+      </c>
+      <c r="D86" s="6" t="inlineStr">
+        <is>
+          <t>Pruebas de rendimiento y carga en produccion (Render)</t>
+        </is>
+      </c>
+      <c r="E86" s="12" t="inlineStr">
+        <is>
+          <t>Marco</t>
+        </is>
+      </c>
+      <c r="F86" s="10" t="n">
+        <v>46144</v>
+      </c>
+      <c r="G86" s="10" t="n">
+        <v>46156</v>
+      </c>
+      <c r="H86" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="I86" s="8" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="J86" s="11" t="inlineStr">
+        <is>
+          <t>Completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="24" customHeight="1">
+      <c r="A87" s="15" t="n"/>
+      <c r="B87" s="16" t="inlineStr">
+        <is>
+          <t>Iteracion</t>
+        </is>
+      </c>
+      <c r="C87" s="16" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="D87" s="15" t="inlineStr">
+        <is>
+          <t>v0.8.0 - Version desplegada en Render con dominio publico, SSL, optimizaciones frontend y pruebas de rendimiento</t>
+        </is>
+      </c>
+      <c r="E87" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F87" s="17" t="n">
+        <v>46157</v>
+      </c>
+      <c r="G87" s="17" t="n">
+        <v>46158</v>
+      </c>
+      <c r="H87" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="I87" s="16" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="J87" s="16" t="inlineStr">
+        <is>
+          <t>Lanzado</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="24" customHeight="1">
+      <c r="A88" s="6" t="n"/>
+      <c r="B88" s="7" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="C88" s="8" t="n">
+        <v>89</v>
+      </c>
+      <c r="D88" s="6" t="inlineStr">
+        <is>
+          <t>Revision Ciclo 4: validacion del despliegue, pruebas y rendimiento</t>
+        </is>
+      </c>
+      <c r="E88" s="9" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+      <c r="F88" s="10" t="n">
+        <v>46157</v>
+      </c>
+      <c r="G88" s="10" t="n">
+        <v>46162</v>
+      </c>
+      <c r="H88" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="I88" s="8" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="J88" s="11" t="inlineStr">
+        <is>
+          <t>Completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="24" customHeight="1">
+      <c r="A89" s="15" t="n"/>
+      <c r="B89" s="16" t="inlineStr">
+        <is>
+          <t>Iteracion</t>
+        </is>
+      </c>
+      <c r="C89" s="16" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="D89" s="15" t="inlineStr">
+        <is>
+          <t>v0.9.0 - Validacion post-despliegue completada, rendimiento verificado y ajustes finales de integracion</t>
+        </is>
+      </c>
+      <c r="E89" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F89" s="17" t="n">
+        <v>46163</v>
+      </c>
+      <c r="G89" s="17" t="n">
+        <v>46164</v>
+      </c>
+      <c r="H89" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="I89" s="16" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="J89" s="16" t="inlineStr">
+        <is>
+          <t>Lanzado</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="24" customHeight="1">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>Ciclo 5: Resultados y Documentacion Final</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="n"/>
+      <c r="C90" s="3" t="n"/>
+      <c r="D90" s="3" t="n"/>
+      <c r="E90" s="3" t="n"/>
+      <c r="F90" s="3" t="n"/>
+      <c r="G90" s="3" t="n"/>
+      <c r="H90" s="3" t="n"/>
+      <c r="I90" s="3" t="n"/>
+      <c r="J90" s="3" t="n"/>
+    </row>
+    <row r="91" ht="24" customHeight="1">
+      <c r="A91" s="4" t="inlineStr">
+        <is>
+          <t>Fase 5: Resultados y Documentacion Final</t>
+        </is>
+      </c>
+      <c r="B91" s="5" t="n"/>
+      <c r="C91" s="5" t="n"/>
+      <c r="D91" s="5" t="n"/>
+      <c r="E91" s="5" t="n"/>
+      <c r="F91" s="5" t="n"/>
+      <c r="G91" s="5" t="n"/>
+      <c r="H91" s="5" t="n"/>
+      <c r="I91" s="5" t="n"/>
+      <c r="J91" s="5" t="n"/>
+    </row>
+    <row r="92" ht="24" customHeight="1">
+      <c r="A92" s="6" t="n"/>
+      <c r="B92" s="7" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="C92" s="8" t="n">
+        <v>66</v>
+      </c>
+      <c r="D92" s="6" t="inlineStr">
+        <is>
+          <t>Analisis con URLs reales: Milenio, Reforma, Aristegui, estafas</t>
+        </is>
+      </c>
+      <c r="E92" s="12" t="inlineStr">
+        <is>
+          <t>Marco</t>
+        </is>
+      </c>
+      <c r="F92" s="10" t="n">
+        <v>46163</v>
+      </c>
+      <c r="G92" s="10" t="n">
+        <v>46175</v>
+      </c>
+      <c r="H92" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="I92" s="8" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="J92" s="11" t="inlineStr">
+        <is>
+          <t>Completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="24" customHeight="1">
+      <c r="A93" s="6" t="n"/>
+      <c r="B93" s="7" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="C93" s="8" t="n">
+        <v>67</v>
+      </c>
+      <c r="D93" s="6" t="inlineStr">
+        <is>
+          <t>Diseno responsive: ajustes layout para movil, tablet y escritorio</t>
+        </is>
+      </c>
+      <c r="E93" s="13" t="inlineStr">
+        <is>
+          <t>Luis</t>
+        </is>
+      </c>
+      <c r="F93" s="10" t="n">
+        <v>46163</v>
+      </c>
+      <c r="G93" s="10" t="n">
+        <v>46174</v>
+      </c>
+      <c r="H93" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I93" s="8" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="J93" s="11" t="inlineStr">
+        <is>
+          <t>Completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="24" customHeight="1">
+      <c r="A94" s="6" t="n"/>
+      <c r="B94" s="7" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="C94" s="8" t="n">
+        <v>68</v>
+      </c>
+      <c r="D94" s="6" t="inlineStr">
+        <is>
+          <t>Capitulo 5: Resultados, pruebas, analisis de datos y conclusiones</t>
+        </is>
+      </c>
+      <c r="E94" s="14" t="inlineStr">
+        <is>
+          <t>Ulises</t>
+        </is>
+      </c>
+      <c r="F94" s="10" t="n">
+        <v>46163</v>
+      </c>
+      <c r="G94" s="10" t="n">
+        <v>46176</v>
+      </c>
+      <c r="H94" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="I94" s="8" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="J94" s="11" t="inlineStr">
+        <is>
+          <t>Completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="24" customHeight="1">
+      <c r="A95" s="6" t="n"/>
+      <c r="B95" s="7" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="C95" s="8" t="n">
+        <v>69</v>
+      </c>
+      <c r="D95" s="6" t="inlineStr">
+        <is>
+          <t>Pruebas de regresion post-despliegue y verificacion funcional</t>
+        </is>
+      </c>
+      <c r="E95" s="13" t="inlineStr">
+        <is>
+          <t>Luis</t>
+        </is>
+      </c>
+      <c r="F95" s="10" t="n">
+        <v>46163</v>
+      </c>
+      <c r="G95" s="10" t="n">
+        <v>46175</v>
+      </c>
+      <c r="H95" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="I95" s="8" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="J95" s="11" t="inlineStr">
+        <is>
+          <t>Completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="24" customHeight="1">
+      <c r="A96" s="15" t="n"/>
+      <c r="B96" s="16" t="inlineStr">
+        <is>
+          <t>Iteracion</t>
+        </is>
+      </c>
+      <c r="C96" s="16" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="D96" s="15" t="inlineStr">
+        <is>
+          <t>v0.10.0 - Analisis con URLs reales, diseno responsive, resultados preliminares y pruebas de regresion post-despliegue</t>
+        </is>
+      </c>
+      <c r="E96" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F96" s="17" t="n">
+        <v>46176</v>
+      </c>
+      <c r="G96" s="17" t="n">
+        <v>46177</v>
+      </c>
+      <c r="H96" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="I96" s="16" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="J96" s="16" t="inlineStr">
+        <is>
+          <t>Lanzado</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="24" customHeight="1">
+      <c r="A97" s="6" t="n"/>
+      <c r="B97" s="7" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="C97" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="D97" s="6" t="inlineStr">
+        <is>
+          <t>Correccion errores: timeouts, override de dominios, edge cases URLs</t>
+        </is>
+      </c>
+      <c r="E97" s="12" t="inlineStr">
+        <is>
+          <t>Marco</t>
+        </is>
+      </c>
+      <c r="F97" s="10" t="n">
+        <v>46176</v>
+      </c>
+      <c r="G97" s="10" t="n">
+        <v>46188</v>
+      </c>
+      <c r="H97" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="I97" s="8" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="J97" s="11" t="inlineStr">
+        <is>
+          <t>Completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="24" customHeight="1">
+      <c r="A98" s="6" t="n"/>
+      <c r="B98" s="7" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="C98" s="8" t="n">
+        <v>71</v>
+      </c>
+      <c r="D98" s="6" t="inlineStr">
+        <is>
+          <t>Manual de usuario completo y guia de uso del sistema</t>
+        </is>
+      </c>
+      <c r="E98" s="13" t="inlineStr">
+        <is>
+          <t>Luis</t>
+        </is>
+      </c>
+      <c r="F98" s="10" t="n">
+        <v>46175</v>
+      </c>
+      <c r="G98" s="10" t="n">
+        <v>46186</v>
+      </c>
+      <c r="H98" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I98" s="8" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="J98" s="11" t="inlineStr">
+        <is>
+          <t>Completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="24" customHeight="1">
+      <c r="A99" s="6" t="n"/>
+      <c r="B99" s="7" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="C99" s="8" t="n">
+        <v>72</v>
+      </c>
+      <c r="D99" s="6" t="inlineStr">
+        <is>
+          <t>Introduccion, resumen y abstract en espanol e ingles</t>
+        </is>
+      </c>
+      <c r="E99" s="14" t="inlineStr">
+        <is>
+          <t>Ulises</t>
+        </is>
+      </c>
+      <c r="F99" s="10" t="n">
+        <v>46177</v>
+      </c>
+      <c r="G99" s="10" t="n">
+        <v>46190</v>
+      </c>
+      <c r="H99" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="I99" s="8" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="J99" s="11" t="inlineStr">
+        <is>
+          <t>Completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="24" customHeight="1">
+      <c r="A100" s="6" t="n"/>
+      <c r="B100" s="7" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="C100" s="8" t="n">
+        <v>73</v>
+      </c>
+      <c r="D100" s="6" t="inlineStr">
+        <is>
+          <t>Documentacion tecnica: manual API, arquitectura, despliegue</t>
+        </is>
+      </c>
+      <c r="E100" s="14" t="inlineStr">
+        <is>
+          <t>Ulises</t>
+        </is>
+      </c>
+      <c r="F100" s="10" t="n">
+        <v>46176</v>
+      </c>
+      <c r="G100" s="10" t="n">
+        <v>46188</v>
+      </c>
+      <c r="H100" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="I100" s="8" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="J100" s="11" t="inlineStr">
+        <is>
+          <t>Completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="24" customHeight="1">
+      <c r="A101" s="15" t="n"/>
+      <c r="B101" s="16" t="inlineStr">
+        <is>
+          <t>Iteracion</t>
+        </is>
+      </c>
+      <c r="C101" s="16" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="D101" s="15" t="inlineStr">
+        <is>
+          <t>v1.0.0 - Documentacion completa, manuales, resultados consolidados y version estable del sistema</t>
+        </is>
+      </c>
+      <c r="E101" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F101" s="17" t="n">
+        <v>46189</v>
+      </c>
+      <c r="G101" s="17" t="n">
+        <v>46190</v>
+      </c>
+      <c r="H101" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="I101" s="16" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="J101" s="16" t="inlineStr">
+        <is>
+          <t>Lanzado</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="24" customHeight="1">
+      <c r="A102" s="6" t="n"/>
+      <c r="B102" s="7" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="C102" s="8" t="n">
+        <v>74</v>
+      </c>
+      <c r="D102" s="6" t="inlineStr">
+        <is>
+          <t>Verificacion funcionalidad, pruebas de humo y validacion URLs reales</t>
+        </is>
+      </c>
+      <c r="E102" s="12" t="inlineStr">
+        <is>
+          <t>Marco</t>
+        </is>
+      </c>
+      <c r="F102" s="10" t="n">
+        <v>46189</v>
+      </c>
+      <c r="G102" s="10" t="n">
+        <v>46201</v>
+      </c>
+      <c r="H102" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="I102" s="8" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J102" s="11" t="inlineStr">
+        <is>
+          <t>Completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="24" customHeight="1">
+      <c r="A103" s="6" t="n"/>
+      <c r="B103" s="7" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="C103" s="8" t="n">
+        <v>75</v>
+      </c>
+      <c r="D103" s="6" t="inlineStr">
+        <is>
+          <t>Maquetacion tesis Word: estilos, indices, tablas de contenido</t>
+        </is>
+      </c>
+      <c r="E103" s="13" t="inlineStr">
+        <is>
+          <t>Luis</t>
+        </is>
+      </c>
+      <c r="F103" s="10" t="n">
+        <v>46187</v>
+      </c>
+      <c r="G103" s="10" t="n">
+        <v>46198</v>
+      </c>
+      <c r="H103" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I103" s="8" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="J103" s="11" t="inlineStr">
+        <is>
+          <t>Completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="24" customHeight="1">
+      <c r="A104" s="6" t="n"/>
+      <c r="B104" s="7" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="C104" s="8" t="n">
+        <v>76</v>
+      </c>
+      <c r="D104" s="6" t="inlineStr">
+        <is>
+          <t>Revision ortografia, gramatica y consistencia de la tesis</t>
+        </is>
+      </c>
+      <c r="E104" s="14" t="inlineStr">
+        <is>
+          <t>Ulises</t>
+        </is>
+      </c>
+      <c r="F104" s="10" t="n">
+        <v>46191</v>
+      </c>
+      <c r="G104" s="10" t="n">
+        <v>46204</v>
+      </c>
+      <c r="H104" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="I104" s="8" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="J104" s="11" t="inlineStr">
+        <is>
+          <t>Completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="24" customHeight="1">
+      <c r="A105" s="6" t="n"/>
+      <c r="B105" s="7" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="C105" s="8" t="n">
+        <v>77</v>
+      </c>
+      <c r="D105" s="6" t="inlineStr">
+        <is>
+          <t>Correcciones estilo, citas y normas institucionales</t>
+        </is>
+      </c>
+      <c r="E105" s="14" t="inlineStr">
+        <is>
+          <t>Ulises</t>
+        </is>
+      </c>
+      <c r="F105" s="10" t="n">
+        <v>46189</v>
+      </c>
+      <c r="G105" s="10" t="n">
+        <v>46201</v>
+      </c>
+      <c r="H105" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="I105" s="8" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="J105" s="11" t="inlineStr">
+        <is>
+          <t>Completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="24" customHeight="1">
+      <c r="A106" s="15" t="n"/>
+      <c r="B106" s="16" t="inlineStr">
+        <is>
+          <t>Iteracion</t>
+        </is>
+      </c>
+      <c r="C106" s="16" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="D106" s="15" t="inlineStr">
+        <is>
+          <t>v1.1.0 - Revisiones finales, verificacion funcional, maquetacion de tesis y correcciones de estilo</t>
+        </is>
+      </c>
+      <c r="E106" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F106" s="17" t="n">
+        <v>46202</v>
+      </c>
+      <c r="G106" s="17" t="n">
+        <v>46203</v>
+      </c>
+      <c r="H106" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="I106" s="16" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="J106" s="16" t="inlineStr">
+        <is>
+          <t>Lanzado</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="24" customHeight="1">
+      <c r="A107" s="6" t="n"/>
+      <c r="B107" s="7" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="C107" s="8" t="n">
+        <v>78</v>
+      </c>
+      <c r="D107" s="6" t="inlineStr">
+        <is>
+          <t>Revision tecnica tesis: datos, consistencia Capitulos 4-5 y codigo</t>
+        </is>
+      </c>
+      <c r="E107" s="12" t="inlineStr">
+        <is>
+          <t>Marco</t>
+        </is>
+      </c>
+      <c r="F107" s="10" t="n">
+        <v>46202</v>
+      </c>
+      <c r="G107" s="10" t="n">
+        <v>46220</v>
+      </c>
+      <c r="H107" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="I107" s="8" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="J107" s="11" t="inlineStr">
+        <is>
+          <t>Completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="24" customHeight="1">
+      <c r="A108" s="6" t="n"/>
+      <c r="B108" s="7" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="C108" s="8" t="n">
+        <v>79</v>
+      </c>
+      <c r="D108" s="6" t="inlineStr">
+        <is>
+          <t>Material presentacion defensa: diapositivas, demo y resultados</t>
+        </is>
+      </c>
+      <c r="E108" s="13" t="inlineStr">
+        <is>
+          <t>Luis</t>
+        </is>
+      </c>
+      <c r="F108" s="10" t="n">
+        <v>46199</v>
+      </c>
+      <c r="G108" s="10" t="n">
+        <v>46216</v>
+      </c>
+      <c r="H108" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="I108" s="8" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J108" s="11" t="inlineStr">
+        <is>
+          <t>Completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="24" customHeight="1">
+      <c r="A109" s="6" t="n"/>
+      <c r="B109" s="7" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="C109" s="8" t="n">
+        <v>80</v>
+      </c>
+      <c r="D109" s="6" t="inlineStr">
+        <is>
+          <t>Correcciones finales segun retroalimentacion del asesor</t>
+        </is>
+      </c>
+      <c r="E109" s="14" t="inlineStr">
+        <is>
+          <t>Ulises</t>
+        </is>
+      </c>
+      <c r="F109" s="10" t="n">
+        <v>46205</v>
+      </c>
+      <c r="G109" s="10" t="n">
+        <v>46224</v>
+      </c>
+      <c r="H109" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="I109" s="8" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="J109" s="11" t="inlineStr">
+        <is>
+          <t>Completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="24" customHeight="1">
+      <c r="A110" s="6" t="n"/>
+      <c r="B110" s="7" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="C110" s="8" t="n">
+        <v>81</v>
+      </c>
+      <c r="D110" s="6" t="inlineStr">
+        <is>
+          <t>Preparacion defensa tesis: diapositivas, demo en vivo y Q&amp;A</t>
+        </is>
+      </c>
+      <c r="E110" s="13" t="inlineStr">
+        <is>
+          <t>Luis</t>
+        </is>
+      </c>
+      <c r="F110" s="10" t="n">
+        <v>46202</v>
+      </c>
+      <c r="G110" s="10" t="n">
+        <v>46220</v>
+      </c>
+      <c r="H110" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="I110" s="8" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="J110" s="11" t="inlineStr">
+        <is>
+          <t>Completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="24" customHeight="1">
+      <c r="A111" s="6" t="n"/>
+      <c r="B111" s="7" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="C111" s="8" t="n">
+        <v>90</v>
+      </c>
+      <c r="D111" s="6" t="inlineStr">
+        <is>
+          <t>Revision y aprobacion del asesor: validacion final tesis y sistema</t>
+        </is>
+      </c>
+      <c r="E111" s="9" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+      <c r="F111" s="10" t="n">
+        <v>46221</v>
+      </c>
+      <c r="G111" s="10" t="n">
+        <v>46233</v>
+      </c>
+      <c r="H111" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="I111" s="8" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="J111" s="11" t="inlineStr">
+        <is>
+          <t>Completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="24" customHeight="1">
+      <c r="A112" s="6" t="n"/>
+      <c r="B112" s="7" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="C112" s="8" t="n">
+        <v>82</v>
+      </c>
+      <c r="D112" s="6" t="inlineStr">
+        <is>
+          <t>Cierre proyecto: limpieza codigo, README, tag v1.2.0 en git</t>
+        </is>
+      </c>
+      <c r="E112" s="12" t="inlineStr">
+        <is>
+          <t>Marco</t>
+        </is>
+      </c>
+      <c r="F112" s="10" t="n">
+        <v>46234</v>
+      </c>
+      <c r="G112" s="10" t="n">
+        <v>46254</v>
+      </c>
+      <c r="H112" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="I112" s="8" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J112" s="11" t="inlineStr">
+        <is>
+          <t>Completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="24" customHeight="1">
+      <c r="A113" s="6" t="n"/>
+      <c r="B113" s="7" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="C113" s="8" t="n">
+        <v>83</v>
+      </c>
+      <c r="D113" s="6" t="inlineStr">
+        <is>
+          <t>PDF final de tesis (TESIS_VERIFEX.pdf) con formato definitivo</t>
+        </is>
+      </c>
+      <c r="E113" s="13" t="inlineStr">
+        <is>
+          <t>Luis</t>
+        </is>
+      </c>
+      <c r="F113" s="10" t="n">
+        <v>46234</v>
+      </c>
+      <c r="G113" s="10" t="n">
+        <v>46253</v>
+      </c>
+      <c r="H113" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="I113" s="8" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J113" s="11" t="inlineStr">
+        <is>
+          <t>Completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="24" customHeight="1">
+      <c r="A114" s="6" t="n"/>
+      <c r="B114" s="7" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="C114" s="8" t="n">
+        <v>84</v>
+      </c>
+      <c r="D114" s="6" t="inlineStr">
+        <is>
+          <t>Revision final y validacion de entrega segun requisitos</t>
+        </is>
+      </c>
+      <c r="E114" s="14" t="inlineStr">
+        <is>
+          <t>Ulises</t>
+        </is>
+      </c>
+      <c r="F114" s="10" t="n">
+        <v>46234</v>
+      </c>
+      <c r="G114" s="10" t="n">
+        <v>46255</v>
+      </c>
+      <c r="H114" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="I114" s="8" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J114" s="11" t="inlineStr">
+        <is>
+          <t>Completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="24" customHeight="1">
+      <c r="A115" s="6" t="n"/>
+      <c r="B115" s="7" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="C115" s="8" t="n">
+        <v>85</v>
+      </c>
+      <c r="D115" s="6" t="inlineStr">
+        <is>
+          <t>Pruebas finales de humo y validacion de cierre del proyecto</t>
+        </is>
+      </c>
+      <c r="E115" s="13" t="inlineStr">
+        <is>
+          <t>Luis</t>
+        </is>
+      </c>
+      <c r="F115" s="10" t="n">
+        <v>46234</v>
+      </c>
+      <c r="G115" s="10" t="n">
+        <v>46254</v>
+      </c>
+      <c r="H115" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="I115" s="8" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J115" s="11" t="inlineStr">
+        <is>
+          <t>Completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="24" customHeight="1">
+      <c r="A116" s="15" t="n"/>
+      <c r="B116" s="16" t="inlineStr">
+        <is>
+          <t>Iteracion</t>
+        </is>
+      </c>
+      <c r="C116" s="16" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="D116" s="15" t="inlineStr">
+        <is>
+          <t>v1.2.0 - Tesis completa, sistema VERIFEX version final y presentacion de defensa preparada</t>
+        </is>
+      </c>
+      <c r="E116" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F116" s="17" t="n">
+        <v>46255</v>
+      </c>
+      <c r="G116" s="17" t="n">
+        <v>46256</v>
+      </c>
+      <c r="H116" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="I116" s="16" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="J116" s="16" t="inlineStr">
+        <is>
+          <t>Lanzado</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="24" customHeight="1"/>
+    <row r="118" ht="24" customHeight="1"/>
+    <row r="119" ht="24" customHeight="1">
+      <c r="A119" s="18" t="inlineStr">
         <is>
           <t>Leyenda:</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="24" customHeight="1">
-      <c r="A78" s="22" t="inlineStr">
+    <row r="120" ht="24" customHeight="1">
+      <c r="A120" s="19" t="inlineStr">
         <is>
           <t>Marco - Backend, frontend, IA, deploy y pruebas</t>
         </is>
       </c>
-      <c r="B78" s="23" t="n"/>
-      <c r="C78" s="23" t="n"/>
-      <c r="D78" s="23" t="n"/>
-    </row>
-    <row r="79" ht="24" customHeight="1">
-      <c r="A79" s="24" t="inlineStr">
+      <c r="B120" s="20" t="n"/>
+      <c r="C120" s="20" t="n"/>
+      <c r="D120" s="20" t="n"/>
+    </row>
+    <row r="121" ht="24" customHeight="1">
+      <c r="A121" s="21" t="inlineStr">
         <is>
           <t>Luis - Frontend, diseno UI/UX y estilos visuales</t>
         </is>
       </c>
-      <c r="B79" s="25" t="n"/>
-      <c r="C79" s="25" t="n"/>
-      <c r="D79" s="25" t="n"/>
-    </row>
-    <row r="80" ht="24" customHeight="1">
-      <c r="A80" s="26" t="inlineStr">
+      <c r="B121" s="22" t="n"/>
+      <c r="C121" s="22" t="n"/>
+      <c r="D121" s="22" t="n"/>
+    </row>
+    <row r="122" ht="24" customHeight="1">
+      <c r="A122" s="23" t="inlineStr">
         <is>
           <t>Ulises - Documentacion y redaccion de tesis</t>
         </is>
       </c>
-      <c r="B80" s="27" t="n"/>
-      <c r="C80" s="27" t="n"/>
-      <c r="D80" s="27" t="n"/>
-    </row>
-    <row r="81" ht="24" customHeight="1">
-      <c r="A81" s="28" t="inlineStr">
-        <is>
-          <t>Tony - Diagramas UML, documentacion y revision de logica</t>
-        </is>
-      </c>
-      <c r="B81" s="29" t="n"/>
-      <c r="C81" s="29" t="n"/>
-      <c r="D81" s="29" t="n"/>
-    </row>
-    <row r="82" ht="24" customHeight="1">
-      <c r="A82" s="30" t="inlineStr">
+      <c r="B122" s="24" t="n"/>
+      <c r="C122" s="24" t="n"/>
+      <c r="D122" s="24" t="n"/>
+    </row>
+    <row r="123" ht="24" customHeight="1">
+      <c r="A123" s="25" t="inlineStr">
         <is>
           <t>★ Iteracion - Hito de lanzamiento de version</t>
         </is>
       </c>
-      <c r="B82" s="31" t="n"/>
-      <c r="C82" s="31" t="n"/>
-      <c r="D82" s="31" t="n"/>
-    </row>
-    <row r="83" ht="24" customHeight="1">
-      <c r="A83" s="30" t="inlineStr">
+      <c r="B123" s="26" t="n"/>
+      <c r="C123" s="26" t="n"/>
+      <c r="D123" s="26" t="n"/>
+    </row>
+    <row r="124" ht="24" customHeight="1">
+      <c r="A124" s="25" t="inlineStr">
         <is>
           <t>Sprint - Tarea individual con duracion definida</t>
         </is>
       </c>
-      <c r="B83" s="31" t="n"/>
-      <c r="C83" s="31" t="n"/>
-      <c r="D83" s="31" t="n"/>
-    </row>
-    <row r="84" ht="24" customHeight="1">
-      <c r="A84" s="30" t="inlineStr">
+      <c r="B124" s="26" t="n"/>
+      <c r="C124" s="26" t="n"/>
+      <c r="D124" s="26" t="n"/>
+    </row>
+    <row r="125" ht="24" customHeight="1">
+      <c r="A125" s="25" t="inlineStr">
         <is>
           <t>Ciclo - Gran fase del proyecto (agrupacion de fases)</t>
         </is>
       </c>
-      <c r="B84" s="31" t="n"/>
-      <c r="C84" s="31" t="n"/>
-      <c r="D84" s="31" t="n"/>
+      <c r="B125" s="26" t="n"/>
+      <c r="C125" s="26" t="n"/>
+      <c r="D125" s="26" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J75"/>
-  <mergeCells count="19">
-    <mergeCell ref="A81:D81"/>
-    <mergeCell ref="A52:J52"/>
-    <mergeCell ref="A10:J10"/>
-    <mergeCell ref="A19:J19"/>
-    <mergeCell ref="A83:D83"/>
-    <mergeCell ref="A82:D82"/>
-    <mergeCell ref="A60:J60"/>
-    <mergeCell ref="A51:J51"/>
-    <mergeCell ref="A11:J11"/>
-    <mergeCell ref="A79:D79"/>
-    <mergeCell ref="A61:J61"/>
-    <mergeCell ref="A78:D78"/>
+  <autoFilter ref="A1:J116"/>
+  <mergeCells count="18">
+    <mergeCell ref="A120:D120"/>
+    <mergeCell ref="A8:J8"/>
+    <mergeCell ref="A122:D122"/>
+    <mergeCell ref="A9:J9"/>
+    <mergeCell ref="A124:D124"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A42:J42"/>
+    <mergeCell ref="A91:J91"/>
+    <mergeCell ref="A123:D123"/>
+    <mergeCell ref="A26:J26"/>
+    <mergeCell ref="A125:D125"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A72:J72"/>
+    <mergeCell ref="A121:D121"/>
     <mergeCell ref="A25:J25"/>
-    <mergeCell ref="A84:D84"/>
-    <mergeCell ref="A80:D80"/>
-    <mergeCell ref="A18:J18"/>
-    <mergeCell ref="A3:J3"/>
-    <mergeCell ref="A26:J26"/>
-    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A90:J90"/>
+    <mergeCell ref="A41:J41"/>
+    <mergeCell ref="A71:J71"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
